--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8587,10 +8587,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8599,10 +8599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8610,10 +8610,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8622,10 +8622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -22065,10 +22065,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -22077,10 +22077,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -22088,10 +22088,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C692" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D692" s="1">
         <x:v>0</x:v>
@@ -22100,10 +22100,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -32576,10 +32576,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1148" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1148" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1148" s="1">
         <x:v>0</x:v>
@@ -32588,10 +32588,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1148" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1148" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1149" spans="1:7">
@@ -32599,10 +32599,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1149" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1149" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1149" s="1">
         <x:v>0</x:v>
@@ -32611,10 +32611,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1149" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1149" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1150" spans="1:7">
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -43294,10 +43294,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43306,10 +43306,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -43317,10 +43317,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1615" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1615" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1615" s="1">
         <x:v>0</x:v>
@@ -43329,10 +43329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1615" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1615" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1616" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -46169,10 +46169,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1739" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1739" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1739" s="1">
         <x:v>0</x:v>
@@ -46181,10 +46181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1739" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1739" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1740" spans="1:7">
@@ -46192,10 +46192,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1740" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1740" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1740" s="1">
         <x:v>0</x:v>
@@ -46204,10 +46204,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1740" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1740" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1741" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8587,10 +8587,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8599,10 +8599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8610,10 +8610,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8622,10 +8622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -22065,10 +22065,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -22077,10 +22077,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -22088,10 +22088,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C692" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D692" s="1">
         <x:v>0</x:v>
@@ -22100,10 +22100,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -32576,10 +32576,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1148" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1148" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1148" s="1">
         <x:v>0</x:v>
@@ -32588,10 +32588,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1148" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1148" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1149" spans="1:7">
@@ -32599,10 +32599,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1149" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1149" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1149" s="1">
         <x:v>0</x:v>
@@ -32611,10 +32611,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1149" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1149" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1150" spans="1:7">
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -46169,10 +46169,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1739" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1739" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1739" s="1">
         <x:v>0</x:v>
@@ -46181,10 +46181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1739" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1739" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1740" spans="1:7">
@@ -46192,10 +46192,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1740" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1740" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1740" s="1">
         <x:v>0</x:v>
@@ -46204,10 +46204,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1740" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1740" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1741" spans="1:7">
@@ -49688,10 +49688,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1892" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1892" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1892" s="1">
         <x:v>0</x:v>
@@ -49700,10 +49700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1892" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1892" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1893" spans="1:7">
@@ -49711,10 +49711,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1893" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1893" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1893" s="1">
         <x:v>0</x:v>
@@ -49723,10 +49723,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1893" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1893" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1894" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -30437,10 +30437,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30449,10 +30449,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -30460,10 +30460,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1056" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1056" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1056" s="1">
         <x:v>0</x:v>
@@ -30472,10 +30472,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1056" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1056" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1057" spans="1:7">
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -37682,10 +37682,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37694,10 +37694,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -37705,10 +37705,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1371" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1371" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1371" s="1">
         <x:v>0</x:v>
@@ -37717,10 +37717,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1371" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1371" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1372" spans="1:7">
@@ -45824,10 +45824,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1724" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1724" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1724" s="1">
         <x:v>0</x:v>
@@ -45836,10 +45836,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1724" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1724" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1725" spans="1:7">
@@ -45847,10 +45847,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1725" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1725" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1725" s="1">
         <x:v>0</x:v>
@@ -45859,10 +45859,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1725" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1725" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1726" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8587,10 +8587,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8599,10 +8599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8610,10 +8610,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8622,10 +8622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -25561,10 +25561,10 @@
         <x:v>892</x:v>
       </x:c>
       <x:c r="B843" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C843" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D843" s="1">
         <x:v>0</x:v>
@@ -25573,10 +25573,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F843" s="1">
-        <x:v>7300</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G843" s="1">
-        <x:v>84580</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="844" spans="1:7">
@@ -25584,10 +25584,10 @@
         <x:v>892</x:v>
       </x:c>
       <x:c r="B844" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C844" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D844" s="1">
         <x:v>0</x:v>
@@ -25596,10 +25596,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F844" s="1">
-        <x:v>5342</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="G844" s="1">
-        <x:v>5342</x:v>
+        <x:v>84580</x:v>
       </x:c>
     </x:row>
     <x:row r="845" spans="1:7">
@@ -30437,10 +30437,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30449,10 +30449,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -30460,10 +30460,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1056" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1056" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1056" s="1">
         <x:v>0</x:v>
@@ -30472,10 +30472,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1056" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1056" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1057" spans="1:7">
@@ -37682,10 +37682,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37694,10 +37694,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -37705,10 +37705,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1371" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1371" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1371" s="1">
         <x:v>0</x:v>
@@ -37717,10 +37717,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1371" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1371" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1372" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -43294,10 +43294,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43306,10 +43306,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -43317,10 +43317,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1615" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1615" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1615" s="1">
         <x:v>0</x:v>
@@ -43329,10 +43329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1615" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1615" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1616" spans="1:7">
@@ -44076,10 +44076,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44088,10 +44088,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -44099,10 +44099,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1649" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1649" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1649" s="1">
         <x:v>0</x:v>
@@ -44111,10 +44111,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1649" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1649" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1650" spans="1:7">
@@ -44536,10 +44536,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1668" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1668" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1668" s="1">
         <x:v>0</x:v>
@@ -44548,10 +44548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1668" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1668" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1669" spans="1:7">
@@ -44559,10 +44559,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1669" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1669" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1669" s="1">
         <x:v>0</x:v>
@@ -44571,10 +44571,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1669" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1669" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1670" spans="1:7">
@@ -45824,10 +45824,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1724" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1724" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1724" s="1">
         <x:v>0</x:v>
@@ -45836,10 +45836,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1724" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1724" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1725" spans="1:7">
@@ -45847,10 +45847,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1725" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1725" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1725" s="1">
         <x:v>0</x:v>
@@ -45859,10 +45859,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1725" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1725" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1726" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -49688,10 +49688,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1892" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1892" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1892" s="1">
         <x:v>0</x:v>
@@ -49700,10 +49700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1892" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1892" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1893" spans="1:7">
@@ -49711,10 +49711,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1893" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1893" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1893" s="1">
         <x:v>0</x:v>
@@ -49723,10 +49723,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1893" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1893" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1894" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8587,10 +8587,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8599,10 +8599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8610,10 +8610,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8622,10 +8622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -25561,10 +25561,10 @@
         <x:v>892</x:v>
       </x:c>
       <x:c r="B843" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C843" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D843" s="1">
         <x:v>0</x:v>
@@ -25573,10 +25573,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F843" s="1">
-        <x:v>5342</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="G843" s="1">
-        <x:v>5342</x:v>
+        <x:v>84580</x:v>
       </x:c>
     </x:row>
     <x:row r="844" spans="1:7">
@@ -25584,10 +25584,10 @@
         <x:v>892</x:v>
       </x:c>
       <x:c r="B844" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C844" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D844" s="1">
         <x:v>0</x:v>
@@ -25596,10 +25596,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F844" s="1">
-        <x:v>7300</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G844" s="1">
-        <x:v>84580</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="845" spans="1:7">
@@ -32576,10 +32576,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1148" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1148" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1148" s="1">
         <x:v>0</x:v>
@@ -32588,10 +32588,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1148" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1148" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1149" spans="1:7">
@@ -32599,10 +32599,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1149" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1149" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1149" s="1">
         <x:v>0</x:v>
@@ -32611,10 +32611,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1149" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1149" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1150" spans="1:7">
@@ -36302,7 +36302,7 @@
         <x:v>1352</x:v>
       </x:c>
       <x:c r="B1310" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1310" s="1">
         <x:v>0</x:v>
@@ -36314,10 +36314,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1310" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1310" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1311" spans="1:7">
@@ -36325,7 +36325,7 @@
         <x:v>1352</x:v>
       </x:c>
       <x:c r="B1311" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1311" s="1">
         <x:v>0</x:v>
@@ -36337,10 +36337,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1311" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1311" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1312" spans="1:7">
@@ -37682,10 +37682,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37694,10 +37694,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -37705,10 +37705,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1371" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1371" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1371" s="1">
         <x:v>0</x:v>
@@ -37717,10 +37717,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1371" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1371" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1372" spans="1:7">
@@ -41546,7 +41546,7 @@
         <x:v>1577</x:v>
       </x:c>
       <x:c r="B1538" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1538" s="1">
         <x:v>0</x:v>
@@ -41558,10 +41558,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1538" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
       <x:c r="G1538" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
     </x:row>
     <x:row r="1539" spans="1:7">
@@ -41569,7 +41569,7 @@
         <x:v>1577</x:v>
       </x:c>
       <x:c r="B1539" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C1539" s="1">
         <x:v>0</x:v>
@@ -41581,10 +41581,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1539" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1539" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1540" spans="1:7">
@@ -43294,10 +43294,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43306,10 +43306,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -43317,10 +43317,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1615" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1615" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1615" s="1">
         <x:v>0</x:v>
@@ -43329,10 +43329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1615" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1615" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1616" spans="1:7">
@@ -44076,10 +44076,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44088,10 +44088,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -44099,10 +44099,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1649" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1649" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1649" s="1">
         <x:v>0</x:v>
@@ -44111,10 +44111,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1649" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1649" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1650" spans="1:7">
@@ -44536,10 +44536,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1668" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1668" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1668" s="1">
         <x:v>0</x:v>
@@ -44548,10 +44548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1668" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1668" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1669" spans="1:7">
@@ -44559,10 +44559,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1669" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1669" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1669" s="1">
         <x:v>0</x:v>
@@ -44571,10 +44571,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1669" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1669" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1670" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">
@@ -49688,10 +49688,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1892" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1892" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1892" s="1">
         <x:v>0</x:v>
@@ -49700,10 +49700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1892" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1892" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1893" spans="1:7">
@@ -49711,10 +49711,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1893" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1893" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1893" s="1">
         <x:v>0</x:v>
@@ -49723,10 +49723,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1893" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1893" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1894" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -30437,10 +30437,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30449,10 +30449,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -30460,10 +30460,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1056" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1056" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1056" s="1">
         <x:v>0</x:v>
@@ -30472,10 +30472,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1056" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1056" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1057" spans="1:7">
@@ -32576,10 +32576,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1148" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1148" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1148" s="1">
         <x:v>0</x:v>
@@ -32588,10 +32588,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1148" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1148" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1149" spans="1:7">
@@ -32599,10 +32599,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1149" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1149" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1149" s="1">
         <x:v>0</x:v>
@@ -32611,10 +32611,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1149" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1149" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1150" spans="1:7">
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -36302,7 +36302,7 @@
         <x:v>1352</x:v>
       </x:c>
       <x:c r="B1310" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1310" s="1">
         <x:v>0</x:v>
@@ -36314,10 +36314,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1310" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1310" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1311" spans="1:7">
@@ -36325,7 +36325,7 @@
         <x:v>1352</x:v>
       </x:c>
       <x:c r="B1311" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1311" s="1">
         <x:v>0</x:v>
@@ -36337,10 +36337,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1311" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1311" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1312" spans="1:7">
@@ -37682,10 +37682,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37694,10 +37694,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -37705,10 +37705,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1371" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1371" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1371" s="1">
         <x:v>0</x:v>
@@ -37717,10 +37717,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1371" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1371" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1372" spans="1:7">
@@ -41546,7 +41546,7 @@
         <x:v>1577</x:v>
       </x:c>
       <x:c r="B1538" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C1538" s="1">
         <x:v>0</x:v>
@@ -41558,10 +41558,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1538" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1538" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1539" spans="1:7">
@@ -41569,7 +41569,7 @@
         <x:v>1577</x:v>
       </x:c>
       <x:c r="B1539" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1539" s="1">
         <x:v>0</x:v>
@@ -41581,10 +41581,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1539" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
       <x:c r="G1539" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
     </x:row>
     <x:row r="1540" spans="1:7">
@@ -45824,10 +45824,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1724" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1724" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1724" s="1">
         <x:v>0</x:v>
@@ -45836,10 +45836,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1724" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1724" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1725" spans="1:7">
@@ -45847,10 +45847,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1725" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1725" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1725" s="1">
         <x:v>0</x:v>
@@ -45859,10 +45859,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1725" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1725" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1726" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8587,10 +8587,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8599,10 +8599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8610,10 +8610,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8622,10 +8622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -22065,10 +22065,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -22077,10 +22077,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -22088,10 +22088,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C692" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D692" s="1">
         <x:v>0</x:v>
@@ -22100,10 +22100,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -30437,10 +30437,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30449,10 +30449,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -30460,10 +30460,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1056" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1056" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1056" s="1">
         <x:v>0</x:v>
@@ -30472,10 +30472,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1056" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1056" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1057" spans="1:7">
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -45824,10 +45824,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1724" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1724" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1724" s="1">
         <x:v>0</x:v>
@@ -45836,10 +45836,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1724" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1724" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1725" spans="1:7">
@@ -45847,10 +45847,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1725" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1725" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1725" s="1">
         <x:v>0</x:v>
@@ -45859,10 +45859,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1725" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1725" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1726" spans="1:7">
@@ -46169,10 +46169,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1739" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1739" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1739" s="1">
         <x:v>0</x:v>
@@ -46181,10 +46181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1739" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1739" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1740" spans="1:7">
@@ -46192,10 +46192,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1740" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1740" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1740" s="1">
         <x:v>0</x:v>
@@ -46204,10 +46204,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1740" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1740" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1741" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8587,10 +8587,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8599,10 +8599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8610,10 +8610,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8622,10 +8622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -17166,10 +17166,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -17178,10 +17178,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -17189,10 +17189,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B479" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C479" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D479" s="1">
         <x:v>0</x:v>
@@ -17201,10 +17201,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F479" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G479" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="480" spans="1:7">
@@ -22065,10 +22065,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -22077,10 +22077,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -22088,10 +22088,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C692" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D692" s="1">
         <x:v>0</x:v>
@@ -22100,10 +22100,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -32576,10 +32576,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1148" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1148" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1148" s="1">
         <x:v>0</x:v>
@@ -32588,10 +32588,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1148" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1148" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1149" spans="1:7">
@@ -32599,10 +32599,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1149" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1149" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1149" s="1">
         <x:v>0</x:v>
@@ -32611,10 +32611,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1149" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1149" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1150" spans="1:7">
@@ -43294,10 +43294,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43306,10 +43306,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -43317,10 +43317,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1615" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1615" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1615" s="1">
         <x:v>0</x:v>
@@ -43329,10 +43329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1615" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1615" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1616" spans="1:7">
@@ -44076,10 +44076,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44088,10 +44088,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -44099,10 +44099,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1649" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1649" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1649" s="1">
         <x:v>0</x:v>
@@ -44111,10 +44111,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1649" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1649" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1650" spans="1:7">
@@ -44536,10 +44536,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1668" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1668" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1668" s="1">
         <x:v>0</x:v>
@@ -44548,10 +44548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1668" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1668" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1669" spans="1:7">
@@ -44559,10 +44559,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1669" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1669" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1669" s="1">
         <x:v>0</x:v>
@@ -44571,10 +44571,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1669" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1669" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1670" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">
@@ -49688,10 +49688,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1892" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1892" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1892" s="1">
         <x:v>0</x:v>
@@ -49700,10 +49700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1892" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1892" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1893" spans="1:7">
@@ -49711,10 +49711,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1893" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1893" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1893" s="1">
         <x:v>0</x:v>
@@ -49723,10 +49723,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1893" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1893" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1894" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -17166,10 +17166,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -17178,10 +17178,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -17189,10 +17189,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B479" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C479" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D479" s="1">
         <x:v>0</x:v>
@@ -17201,10 +17201,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F479" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G479" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="480" spans="1:7">
@@ -37682,10 +37682,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37694,10 +37694,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -37705,10 +37705,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1371" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1371" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1371" s="1">
         <x:v>0</x:v>
@@ -37717,10 +37717,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1371" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1371" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1372" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -43294,10 +43294,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43306,10 +43306,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -43317,10 +43317,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1615" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1615" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1615" s="1">
         <x:v>0</x:v>
@@ -43329,10 +43329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1615" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1615" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1616" spans="1:7">
@@ -44076,10 +44076,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44088,10 +44088,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -44099,10 +44099,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1649" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1649" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1649" s="1">
         <x:v>0</x:v>
@@ -44111,10 +44111,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1649" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1649" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1650" spans="1:7">
@@ -44536,10 +44536,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1668" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1668" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1668" s="1">
         <x:v>0</x:v>
@@ -44548,10 +44548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1668" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1668" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1669" spans="1:7">
@@ -44559,10 +44559,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1669" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1669" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1669" s="1">
         <x:v>0</x:v>
@@ -44571,10 +44571,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1669" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1669" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1670" spans="1:7">
@@ -46169,10 +46169,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1739" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1739" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1739" s="1">
         <x:v>0</x:v>
@@ -46181,10 +46181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1739" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1739" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1740" spans="1:7">
@@ -46192,10 +46192,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1740" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1740" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1740" s="1">
         <x:v>0</x:v>
@@ -46204,10 +46204,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1740" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1740" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1741" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">
@@ -49688,10 +49688,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1892" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1892" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1892" s="1">
         <x:v>0</x:v>
@@ -49700,10 +49700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1892" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1892" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1893" spans="1:7">
@@ -49711,10 +49711,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1893" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1893" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1893" s="1">
         <x:v>0</x:v>
@@ -49723,10 +49723,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1893" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1893" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1894" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -17166,10 +17166,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -17178,10 +17178,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -17189,10 +17189,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B479" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C479" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D479" s="1">
         <x:v>0</x:v>
@@ -17201,10 +17201,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F479" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G479" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="480" spans="1:7">
@@ -32576,10 +32576,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1148" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1148" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1148" s="1">
         <x:v>0</x:v>
@@ -32588,10 +32588,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1148" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1148" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1149" spans="1:7">
@@ -32599,10 +32599,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1149" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1149" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1149" s="1">
         <x:v>0</x:v>
@@ -32611,10 +32611,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1149" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1149" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1150" spans="1:7">
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -43294,10 +43294,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43306,10 +43306,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -43317,10 +43317,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1615" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1615" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1615" s="1">
         <x:v>0</x:v>
@@ -43329,10 +43329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1615" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1615" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1616" spans="1:7">
@@ -44076,10 +44076,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44088,10 +44088,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -44099,10 +44099,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1649" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1649" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1649" s="1">
         <x:v>0</x:v>
@@ -44111,10 +44111,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1649" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1649" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1650" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -31035,10 +31035,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1081" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1081" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1081" s="1">
         <x:v>0</x:v>
@@ -31047,10 +31047,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1081" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1081" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1082" spans="1:7">
@@ -31058,10 +31058,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1082" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C1082" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1082" s="1">
         <x:v>0</x:v>
@@ -31070,10 +31070,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1082" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1082" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1083" spans="1:7">
@@ -37682,10 +37682,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37694,10 +37694,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -37705,10 +37705,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1371" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1371" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1371" s="1">
         <x:v>0</x:v>
@@ -37717,10 +37717,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1371" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1371" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1372" spans="1:7">
@@ -46169,10 +46169,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1739" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1739" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1739" s="1">
         <x:v>0</x:v>
@@ -46181,10 +46181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1739" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1739" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1740" spans="1:7">
@@ -46192,10 +46192,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1740" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1740" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1740" s="1">
         <x:v>0</x:v>
@@ -46204,10 +46204,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1740" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1740" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1741" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">
@@ -49688,10 +49688,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1892" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1892" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1892" s="1">
         <x:v>0</x:v>
@@ -49700,10 +49700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1892" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1892" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1893" spans="1:7">
@@ -49711,10 +49711,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1893" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1893" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1893" s="1">
         <x:v>0</x:v>
@@ -49723,10 +49723,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1893" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1893" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1894" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8587,10 +8587,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8599,10 +8599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8610,10 +8610,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8622,10 +8622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -17166,10 +17166,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -17178,10 +17178,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -17189,10 +17189,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B479" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C479" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D479" s="1">
         <x:v>0</x:v>
@@ -17201,10 +17201,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F479" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G479" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="480" spans="1:7">
@@ -22065,10 +22065,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -22077,10 +22077,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -22088,10 +22088,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C692" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D692" s="1">
         <x:v>0</x:v>
@@ -22100,10 +22100,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -27332,10 +27332,10 @@
         <x:v>968</x:v>
       </x:c>
       <x:c r="B920" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C920" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D920" s="1">
         <x:v>0</x:v>
@@ -27344,10 +27344,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F920" s="1">
-        <x:v>0</x:v>
+        <x:v>8950</x:v>
       </x:c>
       <x:c r="G920" s="1">
-        <x:v>2500</x:v>
+        <x:v>8950</x:v>
       </x:c>
     </x:row>
     <x:row r="921" spans="1:7">
@@ -27355,10 +27355,10 @@
         <x:v>968</x:v>
       </x:c>
       <x:c r="B921" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C921" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D921" s="1">
         <x:v>0</x:v>
@@ -27367,10 +27367,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F921" s="1">
-        <x:v>8950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G921" s="1">
-        <x:v>8950</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="922" spans="1:7">
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -43294,10 +43294,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43306,10 +43306,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -43317,10 +43317,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1615" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1615" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1615" s="1">
         <x:v>0</x:v>
@@ -43329,10 +43329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1615" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1615" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1616" spans="1:7">
@@ -44076,10 +44076,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44088,10 +44088,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -44099,10 +44099,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1649" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1649" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1649" s="1">
         <x:v>0</x:v>
@@ -44111,10 +44111,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1649" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1649" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1650" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -46169,10 +46169,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1739" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1739" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1739" s="1">
         <x:v>0</x:v>
@@ -46181,10 +46181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1739" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1739" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1740" spans="1:7">
@@ -46192,10 +46192,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1740" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1740" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1740" s="1">
         <x:v>0</x:v>
@@ -46204,10 +46204,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1740" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1740" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1741" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -6589,7 +6589,7 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="C18" s="1">
-        <x:v>7590</x:v>
+        <x:v>10590</x:v>
       </x:c>
       <x:c r="D18" s="1">
         <x:v>0</x:v>
@@ -6601,7 +6601,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G18" s="1">
-        <x:v>7590</x:v>
+        <x:v>10590</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7">
@@ -8245,7 +8245,7 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C90" s="1">
-        <x:v>6500</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="D90" s="1">
         <x:v>0</x:v>
@@ -8257,7 +8257,7 @@
         <x:v>13850</x:v>
       </x:c>
       <x:c r="G90" s="1">
-        <x:v>20350</x:v>
+        <x:v>22850</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:7">
@@ -8587,10 +8587,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8599,10 +8599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8610,10 +8610,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8622,10 +8622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -9073,7 +9073,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C126" s="1">
-        <x:v>40780</x:v>
+        <x:v>41780</x:v>
       </x:c>
       <x:c r="D126" s="1">
         <x:v>0</x:v>
@@ -9085,7 +9085,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G126" s="1">
-        <x:v>40780</x:v>
+        <x:v>41780</x:v>
       </x:c>
     </x:row>
     <x:row r="127" spans="1:7">
@@ -9579,7 +9579,7 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="C148" s="1">
-        <x:v>44000</x:v>
+        <x:v>45000</x:v>
       </x:c>
       <x:c r="D148" s="1">
         <x:v>0</x:v>
@@ -9591,7 +9591,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G148" s="1">
-        <x:v>44000</x:v>
+        <x:v>45000</x:v>
       </x:c>
     </x:row>
     <x:row r="149" spans="1:7">
@@ -12868,7 +12868,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C291" s="1">
-        <x:v>55270</x:v>
+        <x:v>57770</x:v>
       </x:c>
       <x:c r="D291" s="1">
         <x:v>0</x:v>
@@ -12880,7 +12880,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G291" s="1">
-        <x:v>55270</x:v>
+        <x:v>57770</x:v>
       </x:c>
     </x:row>
     <x:row r="292" spans="1:7">
@@ -13811,7 +13811,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C332" s="1">
-        <x:v>22500</x:v>
+        <x:v>23500</x:v>
       </x:c>
       <x:c r="D332" s="1">
         <x:v>0</x:v>
@@ -13823,7 +13823,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G332" s="1">
-        <x:v>22500</x:v>
+        <x:v>23500</x:v>
       </x:c>
     </x:row>
     <x:row r="333" spans="1:7">
@@ -18848,7 +18848,7 @@
         <x:v>76</x:v>
       </x:c>
       <x:c r="C551" s="1">
-        <x:v>15000</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="D551" s="1">
         <x:v>0</x:v>
@@ -18860,7 +18860,7 @@
         <x:v>2500</x:v>
       </x:c>
       <x:c r="G551" s="1">
-        <x:v>17500</x:v>
+        <x:v>22500</x:v>
       </x:c>
     </x:row>
     <x:row r="552" spans="1:7">
@@ -19308,7 +19308,7 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="C571" s="1">
-        <x:v>21500</x:v>
+        <x:v>22500</x:v>
       </x:c>
       <x:c r="D571" s="1">
         <x:v>0</x:v>
@@ -19320,7 +19320,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G571" s="1">
-        <x:v>21500</x:v>
+        <x:v>22500</x:v>
       </x:c>
     </x:row>
     <x:row r="572" spans="1:7">
@@ -19331,7 +19331,7 @@
         <x:v>53</x:v>
       </x:c>
       <x:c r="C572" s="1">
-        <x:v>43500</x:v>
+        <x:v>48500</x:v>
       </x:c>
       <x:c r="D572" s="1">
         <x:v>0</x:v>
@@ -19343,7 +19343,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G572" s="1">
-        <x:v>43500</x:v>
+        <x:v>48500</x:v>
       </x:c>
     </x:row>
     <x:row r="573" spans="1:7">
@@ -19630,7 +19630,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C585" s="1">
-        <x:v>10000</x:v>
+        <x:v>12500</x:v>
       </x:c>
       <x:c r="D585" s="1">
         <x:v>0</x:v>
@@ -19642,7 +19642,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G585" s="1">
-        <x:v>10000</x:v>
+        <x:v>12500</x:v>
       </x:c>
     </x:row>
     <x:row r="586" spans="1:7">
@@ -19952,7 +19952,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C599" s="1">
-        <x:v>7090</x:v>
+        <x:v>8090</x:v>
       </x:c>
       <x:c r="D599" s="1">
         <x:v>0</x:v>
@@ -19964,7 +19964,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G599" s="1">
-        <x:v>7090</x:v>
+        <x:v>8090</x:v>
       </x:c>
     </x:row>
     <x:row r="600" spans="1:7">
@@ -21746,7 +21746,7 @@
         <x:v>49</x:v>
       </x:c>
       <x:c r="C677" s="1">
-        <x:v>10500</x:v>
+        <x:v>11500</x:v>
       </x:c>
       <x:c r="D677" s="1">
         <x:v>0</x:v>
@@ -21758,7 +21758,7 @@
         <x:v>1000</x:v>
       </x:c>
       <x:c r="G677" s="1">
-        <x:v>11500</x:v>
+        <x:v>12500</x:v>
       </x:c>
     </x:row>
     <x:row r="678" spans="1:7">
@@ -22065,10 +22065,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -22077,10 +22077,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -22088,10 +22088,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C692" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D692" s="1">
         <x:v>0</x:v>
@@ -22100,10 +22100,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -22275,7 +22275,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C700" s="1">
-        <x:v>7000</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="D700" s="1">
         <x:v>0</x:v>
@@ -22287,7 +22287,7 @@
         <x:v>1250</x:v>
       </x:c>
       <x:c r="G700" s="1">
-        <x:v>8250</x:v>
+        <x:v>9250</x:v>
       </x:c>
     </x:row>
     <x:row r="701" spans="1:7">
@@ -25541,7 +25541,7 @@
         <x:v>38</x:v>
       </x:c>
       <x:c r="C842" s="1">
-        <x:v>6000</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D842" s="1">
         <x:v>0</x:v>
@@ -25553,7 +25553,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G842" s="1">
-        <x:v>6000</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="843" spans="1:7">
@@ -27332,10 +27332,10 @@
         <x:v>968</x:v>
       </x:c>
       <x:c r="B920" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C920" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D920" s="1">
         <x:v>0</x:v>
@@ -27344,10 +27344,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F920" s="1">
-        <x:v>8950</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G920" s="1">
-        <x:v>8950</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="921" spans="1:7">
@@ -27355,10 +27355,10 @@
         <x:v>968</x:v>
       </x:c>
       <x:c r="B921" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C921" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D921" s="1">
         <x:v>0</x:v>
@@ -27367,10 +27367,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F921" s="1">
-        <x:v>0</x:v>
+        <x:v>8950</x:v>
       </x:c>
       <x:c r="G921" s="1">
-        <x:v>2500</x:v>
+        <x:v>8950</x:v>
       </x:c>
     </x:row>
     <x:row r="922" spans="1:7">
@@ -28094,7 +28094,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C953" s="1">
-        <x:v>18500</x:v>
+        <x:v>19500</x:v>
       </x:c>
       <x:c r="D953" s="1">
         <x:v>0</x:v>
@@ -28106,7 +28106,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G953" s="1">
-        <x:v>18500</x:v>
+        <x:v>19500</x:v>
       </x:c>
     </x:row>
     <x:row r="954" spans="1:7">
@@ -28761,7 +28761,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C982" s="1">
-        <x:v>2000</x:v>
+        <x:v>5500</x:v>
       </x:c>
       <x:c r="D982" s="1">
         <x:v>0</x:v>
@@ -28773,7 +28773,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G982" s="1">
-        <x:v>2000</x:v>
+        <x:v>5500</x:v>
       </x:c>
     </x:row>
     <x:row r="983" spans="1:7">
@@ -29520,7 +29520,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C1015" s="1">
-        <x:v>3000</x:v>
+        <x:v>4000</x:v>
       </x:c>
       <x:c r="D1015" s="1">
         <x:v>0</x:v>
@@ -29532,7 +29532,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1015" s="1">
-        <x:v>3000</x:v>
+        <x:v>4000</x:v>
       </x:c>
     </x:row>
     <x:row r="1016" spans="1:7">
@@ -30026,7 +30026,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C1037" s="1">
-        <x:v>18000</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="D1037" s="1">
         <x:v>0</x:v>
@@ -30038,7 +30038,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1037" s="1">
-        <x:v>18000</x:v>
+        <x:v>20000</x:v>
       </x:c>
     </x:row>
     <x:row r="1038" spans="1:7">
@@ -31035,10 +31035,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1081" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C1081" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1081" s="1">
         <x:v>0</x:v>
@@ -31047,10 +31047,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1081" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1081" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1082" spans="1:7">
@@ -31058,10 +31058,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1082" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1082" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1082" s="1">
         <x:v>0</x:v>
@@ -31070,10 +31070,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1082" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1082" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1083" spans="1:7">
@@ -31935,7 +31935,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C1120" s="1">
-        <x:v>23635</x:v>
+        <x:v>33635</x:v>
       </x:c>
       <x:c r="D1120" s="1">
         <x:v>0</x:v>
@@ -31947,7 +31947,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1120" s="1">
-        <x:v>23635</x:v>
+        <x:v>33635</x:v>
       </x:c>
     </x:row>
     <x:row r="1121" spans="1:7">
@@ -32786,7 +32786,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C1157" s="1">
-        <x:v>6230</x:v>
+        <x:v>7230</x:v>
       </x:c>
       <x:c r="D1157" s="1">
         <x:v>0</x:v>
@@ -32798,7 +32798,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1157" s="1">
-        <x:v>6230</x:v>
+        <x:v>7230</x:v>
       </x:c>
     </x:row>
     <x:row r="1158" spans="1:7">
@@ -33913,7 +33913,7 @@
         <x:v>282</x:v>
       </x:c>
       <x:c r="C1206" s="1">
-        <x:v>15000</x:v>
+        <x:v>17500</x:v>
       </x:c>
       <x:c r="D1206" s="1">
         <x:v>0</x:v>
@@ -33925,7 +33925,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1206" s="1">
-        <x:v>15000</x:v>
+        <x:v>17500</x:v>
       </x:c>
     </x:row>
     <x:row r="1207" spans="1:7">
@@ -34442,7 +34442,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C1229" s="1">
-        <x:v>25500</x:v>
+        <x:v>26500</x:v>
       </x:c>
       <x:c r="D1229" s="1">
         <x:v>0</x:v>
@@ -34454,7 +34454,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1229" s="1">
-        <x:v>25500</x:v>
+        <x:v>26500</x:v>
       </x:c>
     </x:row>
     <x:row r="1230" spans="1:7">
@@ -35799,7 +35799,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C1288" s="1">
-        <x:v>6500</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1288" s="1">
         <x:v>0</x:v>
@@ -35811,7 +35811,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1288" s="1">
-        <x:v>6500</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1289" spans="1:7">
@@ -36144,7 +36144,7 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="C1303" s="1">
-        <x:v>23000</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1303" s="1">
         <x:v>0</x:v>
@@ -36156,7 +36156,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1303" s="1">
-        <x:v>23000</x:v>
+        <x:v>24000</x:v>
       </x:c>
     </x:row>
     <x:row r="1304" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -42216,7 +42216,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="C1567" s="1">
-        <x:v>9000</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="D1567" s="1">
         <x:v>0</x:v>
@@ -42228,7 +42228,7 @@
         <x:v>3300</x:v>
       </x:c>
       <x:c r="G1567" s="1">
-        <x:v>12300</x:v>
+        <x:v>13300</x:v>
       </x:c>
     </x:row>
     <x:row r="1568" spans="1:7">
@@ -44424,7 +44424,7 @@
         <x:v>108</x:v>
       </x:c>
       <x:c r="C1663" s="1">
-        <x:v>60000</x:v>
+        <x:v>65000</x:v>
       </x:c>
       <x:c r="D1663" s="1">
         <x:v>0</x:v>
@@ -44436,7 +44436,7 @@
         <x:v>8000</x:v>
       </x:c>
       <x:c r="G1663" s="1">
-        <x:v>68000</x:v>
+        <x:v>73000</x:v>
       </x:c>
     </x:row>
     <x:row r="1664" spans="1:7">
@@ -45091,7 +45091,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="C1692" s="1">
-        <x:v>18500</x:v>
+        <x:v>23500</x:v>
       </x:c>
       <x:c r="D1692" s="1">
         <x:v>0</x:v>
@@ -45103,7 +45103,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1692" s="1">
-        <x:v>18500</x:v>
+        <x:v>23500</x:v>
       </x:c>
     </x:row>
     <x:row r="1693" spans="1:7">
@@ -45804,7 +45804,7 @@
         <x:v>360</x:v>
       </x:c>
       <x:c r="C1723" s="1">
-        <x:v>127500</x:v>
+        <x:v>130000</x:v>
       </x:c>
       <x:c r="D1723" s="1">
         <x:v>0</x:v>
@@ -45816,7 +45816,7 @@
         <x:v>7474</x:v>
       </x:c>
       <x:c r="G1723" s="1">
-        <x:v>134974</x:v>
+        <x:v>137474</x:v>
       </x:c>
     </x:row>
     <x:row r="1724" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -46678,7 +46678,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C1761" s="1">
-        <x:v>7000</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="D1761" s="1">
         <x:v>0</x:v>
@@ -46690,7 +46690,7 @@
         <x:v>500</x:v>
       </x:c>
       <x:c r="G1761" s="1">
-        <x:v>7500</x:v>
+        <x:v>9500</x:v>
       </x:c>
     </x:row>
     <x:row r="1762" spans="1:7">
@@ -47368,7 +47368,7 @@
         <x:v>177</x:v>
       </x:c>
       <x:c r="C1791" s="1">
-        <x:v>10000</x:v>
+        <x:v>12000</x:v>
       </x:c>
       <x:c r="D1791" s="1">
         <x:v>0</x:v>
@@ -47380,7 +47380,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1791" s="1">
-        <x:v>10000</x:v>
+        <x:v>12000</x:v>
       </x:c>
     </x:row>
     <x:row r="1792" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">
@@ -48679,7 +48679,7 @@
         <x:v>166</x:v>
       </x:c>
       <x:c r="C1848" s="1">
-        <x:v>37000</x:v>
+        <x:v>38000</x:v>
       </x:c>
       <x:c r="D1848" s="1">
         <x:v>0</x:v>
@@ -48691,7 +48691,7 @@
         <x:v>1600</x:v>
       </x:c>
       <x:c r="G1848" s="1">
-        <x:v>38600</x:v>
+        <x:v>39600</x:v>
       </x:c>
     </x:row>
     <x:row r="1849" spans="1:7">
@@ -48794,7 +48794,7 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="C1853" s="1">
-        <x:v>8000</x:v>
+        <x:v>10000</x:v>
       </x:c>
       <x:c r="D1853" s="1">
         <x:v>0</x:v>
@@ -48806,7 +48806,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1853" s="1">
-        <x:v>8000</x:v>
+        <x:v>10000</x:v>
       </x:c>
     </x:row>
     <x:row r="1854" spans="1:7">
@@ -49346,7 +49346,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C1877" s="1">
-        <x:v>67180</x:v>
+        <x:v>69680</x:v>
       </x:c>
       <x:c r="D1877" s="1">
         <x:v>0</x:v>
@@ -49358,7 +49358,7 @@
         <x:v>1500</x:v>
       </x:c>
       <x:c r="G1877" s="1">
-        <x:v>68680</x:v>
+        <x:v>71180</x:v>
       </x:c>
     </x:row>
     <x:row r="1878" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8587,10 +8587,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8599,10 +8599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8610,10 +8610,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8622,10 +8622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -30437,10 +30437,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30449,10 +30449,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -30460,10 +30460,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1056" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1056" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1056" s="1">
         <x:v>0</x:v>
@@ -30472,10 +30472,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1056" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1056" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1057" spans="1:7">
@@ -37682,10 +37682,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37694,10 +37694,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -37705,10 +37705,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1371" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1371" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1371" s="1">
         <x:v>0</x:v>
@@ -37717,10 +37717,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1371" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1371" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1372" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -45824,10 +45824,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1724" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1724" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1724" s="1">
         <x:v>0</x:v>
@@ -45836,10 +45836,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1724" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1724" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1725" spans="1:7">
@@ -45847,10 +45847,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1725" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1725" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1725" s="1">
         <x:v>0</x:v>
@@ -45859,10 +45859,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1725" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1725" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1726" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -46169,10 +46169,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1739" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1739" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1739" s="1">
         <x:v>0</x:v>
@@ -46181,10 +46181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1739" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1739" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1740" spans="1:7">
@@ -46192,10 +46192,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1740" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1740" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1740" s="1">
         <x:v>0</x:v>
@@ -46204,10 +46204,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1740" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1740" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1741" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8587,10 +8587,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8599,10 +8599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8610,10 +8610,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8622,10 +8622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -17166,10 +17166,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -17178,10 +17178,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -17189,10 +17189,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B479" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C479" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D479" s="1">
         <x:v>0</x:v>
@@ -17201,10 +17201,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F479" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G479" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="480" spans="1:7">
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -17166,10 +17166,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -17178,10 +17178,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -17189,10 +17189,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B479" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C479" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D479" s="1">
         <x:v>0</x:v>
@@ -17201,10 +17201,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F479" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G479" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="480" spans="1:7">
@@ -30437,10 +30437,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30449,10 +30449,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -30460,10 +30460,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1056" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1056" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1056" s="1">
         <x:v>0</x:v>
@@ -30472,10 +30472,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1056" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1056" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1057" spans="1:7">
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -37682,10 +37682,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37694,10 +37694,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -37705,10 +37705,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1371" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1371" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1371" s="1">
         <x:v>0</x:v>
@@ -37717,10 +37717,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1371" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1371" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1372" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -45824,10 +45824,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1724" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1724" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1724" s="1">
         <x:v>0</x:v>
@@ -45836,10 +45836,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1724" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1724" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1725" spans="1:7">
@@ -45847,10 +45847,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1725" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1725" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1725" s="1">
         <x:v>0</x:v>
@@ -45859,10 +45859,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1725" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1725" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1726" spans="1:7">
@@ -46169,10 +46169,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1739" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1739" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1739" s="1">
         <x:v>0</x:v>
@@ -46181,10 +46181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1739" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1739" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1740" spans="1:7">
@@ -46192,10 +46192,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1740" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1740" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1740" s="1">
         <x:v>0</x:v>
@@ -46204,10 +46204,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1740" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1740" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1741" spans="1:7">
@@ -49688,10 +49688,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1892" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1892" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1892" s="1">
         <x:v>0</x:v>
@@ -49700,10 +49700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1892" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1892" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1893" spans="1:7">
@@ -49711,10 +49711,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1893" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1893" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1893" s="1">
         <x:v>0</x:v>
@@ -49723,10 +49723,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1893" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1893" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1894" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -30437,10 +30437,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30449,10 +30449,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -30460,10 +30460,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1056" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1056" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1056" s="1">
         <x:v>0</x:v>
@@ -30472,10 +30472,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1056" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1056" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1057" spans="1:7">
@@ -31035,10 +31035,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1081" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1081" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1081" s="1">
         <x:v>0</x:v>
@@ -31047,10 +31047,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1081" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1081" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1082" spans="1:7">
@@ -31058,10 +31058,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1082" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C1082" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1082" s="1">
         <x:v>0</x:v>
@@ -31070,10 +31070,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1082" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1082" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1083" spans="1:7">
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -37682,10 +37682,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37694,10 +37694,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -37705,10 +37705,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1371" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1371" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1371" s="1">
         <x:v>0</x:v>
@@ -37717,10 +37717,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1371" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1371" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1372" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -43294,10 +43294,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43306,10 +43306,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -43317,10 +43317,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1615" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1615" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1615" s="1">
         <x:v>0</x:v>
@@ -43329,10 +43329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1615" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1615" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1616" spans="1:7">
@@ -45824,10 +45824,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1724" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1724" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1724" s="1">
         <x:v>0</x:v>
@@ -45836,10 +45836,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1724" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1724" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1725" spans="1:7">
@@ -45847,10 +45847,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1725" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1725" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1725" s="1">
         <x:v>0</x:v>
@@ -45859,10 +45859,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1725" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1725" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1726" spans="1:7">
@@ -49688,10 +49688,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1892" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1892" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1892" s="1">
         <x:v>0</x:v>
@@ -49700,10 +49700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1892" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1892" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1893" spans="1:7">
@@ -49711,10 +49711,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1893" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1893" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1893" s="1">
         <x:v>0</x:v>
@@ -49723,10 +49723,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1893" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1893" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1894" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8587,10 +8587,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8599,10 +8599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8610,10 +8610,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8622,10 +8622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -25561,10 +25561,10 @@
         <x:v>892</x:v>
       </x:c>
       <x:c r="B843" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C843" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D843" s="1">
         <x:v>0</x:v>
@@ -25573,10 +25573,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F843" s="1">
-        <x:v>7300</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G843" s="1">
-        <x:v>84580</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="844" spans="1:7">
@@ -25584,10 +25584,10 @@
         <x:v>892</x:v>
       </x:c>
       <x:c r="B844" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C844" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D844" s="1">
         <x:v>0</x:v>
@@ -25596,10 +25596,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F844" s="1">
-        <x:v>5342</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="G844" s="1">
-        <x:v>5342</x:v>
+        <x:v>84580</x:v>
       </x:c>
     </x:row>
     <x:row r="845" spans="1:7">
@@ -30437,10 +30437,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30449,10 +30449,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -30460,10 +30460,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1056" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1056" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1056" s="1">
         <x:v>0</x:v>
@@ -30472,10 +30472,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1056" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1056" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1057" spans="1:7">
@@ -31035,10 +31035,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1081" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C1081" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1081" s="1">
         <x:v>0</x:v>
@@ -31047,10 +31047,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1081" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1081" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1082" spans="1:7">
@@ -31058,10 +31058,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1082" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1082" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1082" s="1">
         <x:v>0</x:v>
@@ -31070,10 +31070,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1082" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1082" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1083" spans="1:7">
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -37682,10 +37682,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37694,10 +37694,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -37705,10 +37705,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1371" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1371" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1371" s="1">
         <x:v>0</x:v>
@@ -37717,10 +37717,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1371" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1371" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1372" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -43294,10 +43294,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43306,10 +43306,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -43317,10 +43317,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1615" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1615" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1615" s="1">
         <x:v>0</x:v>
@@ -43329,10 +43329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1615" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1615" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1616" spans="1:7">
@@ -44536,10 +44536,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1668" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1668" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1668" s="1">
         <x:v>0</x:v>
@@ -44548,10 +44548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1668" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1668" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1669" spans="1:7">
@@ -44559,10 +44559,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1669" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1669" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1669" s="1">
         <x:v>0</x:v>
@@ -44571,10 +44571,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1669" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1669" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1670" spans="1:7">
@@ -45824,10 +45824,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1724" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1724" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1724" s="1">
         <x:v>0</x:v>
@@ -45836,10 +45836,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1724" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1724" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1725" spans="1:7">
@@ -45847,10 +45847,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1725" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1725" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1725" s="1">
         <x:v>0</x:v>
@@ -45859,10 +45859,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1725" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1725" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1726" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">
@@ -49688,10 +49688,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1892" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1892" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1892" s="1">
         <x:v>0</x:v>
@@ -49700,10 +49700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1892" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1892" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1893" spans="1:7">
@@ -49711,10 +49711,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1893" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1893" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1893" s="1">
         <x:v>0</x:v>
@@ -49723,10 +49723,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1893" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1893" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1894" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8587,10 +8587,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8599,10 +8599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8610,10 +8610,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8622,10 +8622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -19167,7 +19167,7 @@
         <x:v>618</x:v>
       </x:c>
       <x:c r="B565" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C565" s="1">
         <x:v>0</x:v>
@@ -19179,10 +19179,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F565" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="G565" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
     </x:row>
     <x:row r="566" spans="1:7">
@@ -19190,7 +19190,7 @@
         <x:v>618</x:v>
       </x:c>
       <x:c r="B566" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C566" s="1">
         <x:v>0</x:v>
@@ -19202,10 +19202,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F566" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
       <x:c r="G566" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
     </x:row>
     <x:row r="567" spans="1:7">
@@ -25561,10 +25561,10 @@
         <x:v>892</x:v>
       </x:c>
       <x:c r="B843" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C843" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D843" s="1">
         <x:v>0</x:v>
@@ -25573,10 +25573,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F843" s="1">
-        <x:v>5342</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="G843" s="1">
-        <x:v>5342</x:v>
+        <x:v>84580</x:v>
       </x:c>
     </x:row>
     <x:row r="844" spans="1:7">
@@ -25584,10 +25584,10 @@
         <x:v>892</x:v>
       </x:c>
       <x:c r="B844" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C844" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D844" s="1">
         <x:v>0</x:v>
@@ -25596,10 +25596,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F844" s="1">
-        <x:v>7300</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G844" s="1">
-        <x:v>84580</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="845" spans="1:7">
@@ -31035,10 +31035,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1081" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1081" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1081" s="1">
         <x:v>0</x:v>
@@ -31047,10 +31047,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1081" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1081" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1082" spans="1:7">
@@ -31058,10 +31058,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1082" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C1082" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1082" s="1">
         <x:v>0</x:v>
@@ -31070,10 +31070,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1082" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1082" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1083" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -44536,10 +44536,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1668" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1668" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1668" s="1">
         <x:v>0</x:v>
@@ -44548,10 +44548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1668" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1668" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1669" spans="1:7">
@@ -44559,10 +44559,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1669" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1669" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1669" s="1">
         <x:v>0</x:v>
@@ -44571,10 +44571,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1669" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1669" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1670" spans="1:7">
@@ -46169,10 +46169,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1739" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1739" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1739" s="1">
         <x:v>0</x:v>
@@ -46181,10 +46181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1739" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1739" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1740" spans="1:7">
@@ -46192,10 +46192,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1740" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1740" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1740" s="1">
         <x:v>0</x:v>
@@ -46204,10 +46204,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1740" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1740" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1741" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">
@@ -49688,10 +49688,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1892" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1892" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1892" s="1">
         <x:v>0</x:v>
@@ -49700,10 +49700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1892" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1892" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1893" spans="1:7">
@@ -49711,10 +49711,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1893" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1893" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1893" s="1">
         <x:v>0</x:v>
@@ -49723,10 +49723,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1893" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1893" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1894" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8728,7 +8728,7 @@
         <x:v>87</x:v>
       </x:c>
       <x:c r="C111" s="1">
-        <x:v>9000</x:v>
+        <x:v>14000</x:v>
       </x:c>
       <x:c r="D111" s="1">
         <x:v>0</x:v>
@@ -8740,7 +8740,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G111" s="1">
-        <x:v>9000</x:v>
+        <x:v>14000</x:v>
       </x:c>
     </x:row>
     <x:row r="112" spans="1:7">
@@ -13811,7 +13811,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="C332" s="1">
-        <x:v>23500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D332" s="1">
         <x:v>0</x:v>
@@ -13823,7 +13823,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G332" s="1">
-        <x:v>23500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="333" spans="1:7">
@@ -16042,7 +16042,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="C429" s="1">
-        <x:v>9000</x:v>
+        <x:v>8000</x:v>
       </x:c>
       <x:c r="D429" s="1">
         <x:v>0</x:v>
@@ -16054,7 +16054,7 @@
         <x:v>3250</x:v>
       </x:c>
       <x:c r="G429" s="1">
-        <x:v>12250</x:v>
+        <x:v>11250</x:v>
       </x:c>
     </x:row>
     <x:row r="430" spans="1:7">
@@ -17166,10 +17166,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -17178,10 +17178,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -17189,10 +17189,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B479" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C479" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D479" s="1">
         <x:v>0</x:v>
@@ -17201,10 +17201,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F479" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G479" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="480" spans="1:7">
@@ -19167,7 +19167,7 @@
         <x:v>618</x:v>
       </x:c>
       <x:c r="B565" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C565" s="1">
         <x:v>0</x:v>
@@ -19179,10 +19179,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F565" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
       <x:c r="G565" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
     </x:row>
     <x:row r="566" spans="1:7">
@@ -19190,7 +19190,7 @@
         <x:v>618</x:v>
       </x:c>
       <x:c r="B566" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C566" s="1">
         <x:v>0</x:v>
@@ -19202,10 +19202,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F566" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="G566" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
     </x:row>
     <x:row r="567" spans="1:7">
@@ -19952,7 +19952,7 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="C599" s="1">
-        <x:v>8090</x:v>
+        <x:v>9090</x:v>
       </x:c>
       <x:c r="D599" s="1">
         <x:v>0</x:v>
@@ -19964,7 +19964,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G599" s="1">
-        <x:v>8090</x:v>
+        <x:v>9090</x:v>
       </x:c>
     </x:row>
     <x:row r="600" spans="1:7">
@@ -27703,7 +27703,7 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="C936" s="1">
-        <x:v>67000</x:v>
+        <x:v>66500</x:v>
       </x:c>
       <x:c r="D936" s="1">
         <x:v>0</x:v>
@@ -27715,7 +27715,7 @@
         <x:v>6750</x:v>
       </x:c>
       <x:c r="G936" s="1">
-        <x:v>73750</x:v>
+        <x:v>73250</x:v>
       </x:c>
     </x:row>
     <x:row r="937" spans="1:7">
@@ -32576,10 +32576,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1148" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1148" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1148" s="1">
         <x:v>0</x:v>
@@ -32588,10 +32588,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1148" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1148" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1149" spans="1:7">
@@ -32599,10 +32599,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1149" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1149" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1149" s="1">
         <x:v>0</x:v>
@@ -32611,10 +32611,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1149" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1149" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1150" spans="1:7">
@@ -34741,7 +34741,7 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="C1242" s="1">
-        <x:v>11500</x:v>
+        <x:v>9000</x:v>
       </x:c>
       <x:c r="D1242" s="1">
         <x:v>0</x:v>
@@ -34753,7 +34753,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1242" s="1">
-        <x:v>11500</x:v>
+        <x:v>9000</x:v>
       </x:c>
     </x:row>
     <x:row r="1243" spans="1:7">
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -37682,10 +37682,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37694,10 +37694,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -37705,10 +37705,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1371" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1371" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1371" s="1">
         <x:v>0</x:v>
@@ -37717,10 +37717,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1371" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1371" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1372" spans="1:7">
@@ -40514,7 +40514,7 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="C1493" s="1">
-        <x:v>48000</x:v>
+        <x:v>51000</x:v>
       </x:c>
       <x:c r="D1493" s="1">
         <x:v>0</x:v>
@@ -40526,7 +40526,7 @@
         <x:v>20500</x:v>
       </x:c>
       <x:c r="G1493" s="1">
-        <x:v>68500</x:v>
+        <x:v>71500</x:v>
       </x:c>
     </x:row>
     <x:row r="1494" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -43294,10 +43294,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43306,10 +43306,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -43317,10 +43317,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1615" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1615" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1615" s="1">
         <x:v>0</x:v>
@@ -43329,10 +43329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1615" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1615" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1616" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -17166,10 +17166,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -17178,10 +17178,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -17189,10 +17189,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B479" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C479" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D479" s="1">
         <x:v>0</x:v>
@@ -17201,10 +17201,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F479" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G479" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="480" spans="1:7">
@@ -31035,10 +31035,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1081" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C1081" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1081" s="1">
         <x:v>0</x:v>
@@ -31047,10 +31047,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1081" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1081" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1082" spans="1:7">
@@ -31058,10 +31058,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1082" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1082" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1082" s="1">
         <x:v>0</x:v>
@@ -31070,10 +31070,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1082" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1082" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1083" spans="1:7">
@@ -32576,10 +32576,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1148" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1148" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1148" s="1">
         <x:v>0</x:v>
@@ -32588,10 +32588,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1148" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1148" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1149" spans="1:7">
@@ -32599,10 +32599,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1149" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1149" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1149" s="1">
         <x:v>0</x:v>
@@ -32611,10 +32611,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1149" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1149" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1150" spans="1:7">
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -46169,10 +46169,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1739" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1739" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1739" s="1">
         <x:v>0</x:v>
@@ -46181,10 +46181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1739" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1739" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1740" spans="1:7">
@@ -46192,10 +46192,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1740" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1740" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1740" s="1">
         <x:v>0</x:v>
@@ -46204,10 +46204,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1740" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1740" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1741" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -31035,10 +31035,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1081" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1081" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1081" s="1">
         <x:v>0</x:v>
@@ -31047,10 +31047,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1081" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1081" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1082" spans="1:7">
@@ -31058,10 +31058,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1082" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C1082" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1082" s="1">
         <x:v>0</x:v>
@@ -31070,10 +31070,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1082" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1082" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1083" spans="1:7">
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -37682,10 +37682,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37694,10 +37694,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -37705,10 +37705,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1371" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1371" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1371" s="1">
         <x:v>0</x:v>
@@ -37717,10 +37717,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1371" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1371" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1372" spans="1:7">
@@ -44076,10 +44076,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44088,10 +44088,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -44099,10 +44099,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1649" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1649" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1649" s="1">
         <x:v>0</x:v>
@@ -44111,10 +44111,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1649" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1649" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1650" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -46169,10 +46169,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1739" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1739" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1739" s="1">
         <x:v>0</x:v>
@@ -46181,10 +46181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1739" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1739" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1740" spans="1:7">
@@ -46192,10 +46192,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1740" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1740" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1740" s="1">
         <x:v>0</x:v>
@@ -46204,10 +46204,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1740" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1740" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1741" spans="1:7">
@@ -49688,10 +49688,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1892" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1892" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1892" s="1">
         <x:v>0</x:v>
@@ -49700,10 +49700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1892" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1892" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1893" spans="1:7">
@@ -49711,10 +49711,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1893" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1893" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1893" s="1">
         <x:v>0</x:v>
@@ -49723,10 +49723,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1893" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1893" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1894" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -32576,10 +32576,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1148" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1148" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1148" s="1">
         <x:v>0</x:v>
@@ -32588,10 +32588,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1148" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1148" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1149" spans="1:7">
@@ -32599,10 +32599,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1149" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1149" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1149" s="1">
         <x:v>0</x:v>
@@ -32611,10 +32611,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1149" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1149" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1150" spans="1:7">
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -43294,10 +43294,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43306,10 +43306,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -43317,10 +43317,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1615" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1615" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1615" s="1">
         <x:v>0</x:v>
@@ -43329,10 +43329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1615" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1615" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1616" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -46169,10 +46169,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1739" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1739" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1739" s="1">
         <x:v>0</x:v>
@@ -46181,10 +46181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1739" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1739" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1740" spans="1:7">
@@ -46192,10 +46192,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1740" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1740" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1740" s="1">
         <x:v>0</x:v>
@@ -46204,10 +46204,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1740" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1740" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1741" spans="1:7">
@@ -49688,10 +49688,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1892" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1892" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1892" s="1">
         <x:v>0</x:v>
@@ -49700,10 +49700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1892" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1892" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1893" spans="1:7">
@@ -49711,10 +49711,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1893" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1893" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1893" s="1">
         <x:v>0</x:v>
@@ -49723,10 +49723,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1893" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1893" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1894" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8587,10 +8587,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8599,10 +8599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8610,10 +8610,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8622,10 +8622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -31035,10 +31035,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1081" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C1081" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1081" s="1">
         <x:v>0</x:v>
@@ -31047,10 +31047,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1081" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1081" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1082" spans="1:7">
@@ -31058,10 +31058,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1082" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1082" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1082" s="1">
         <x:v>0</x:v>
@@ -31070,10 +31070,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1082" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1082" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1083" spans="1:7">
@@ -32576,10 +32576,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1148" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1148" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1148" s="1">
         <x:v>0</x:v>
@@ -32588,10 +32588,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1148" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1148" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1149" spans="1:7">
@@ -32599,10 +32599,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1149" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1149" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1149" s="1">
         <x:v>0</x:v>
@@ -32611,10 +32611,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1149" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1149" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1150" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -43294,10 +43294,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43306,10 +43306,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -43317,10 +43317,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1615" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1615" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1615" s="1">
         <x:v>0</x:v>
@@ -43329,10 +43329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1615" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1615" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1616" spans="1:7">
@@ -46169,10 +46169,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1739" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1739" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1739" s="1">
         <x:v>0</x:v>
@@ -46181,10 +46181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1739" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1739" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1740" spans="1:7">
@@ -46192,10 +46192,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1740" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1740" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1740" s="1">
         <x:v>0</x:v>
@@ -46204,10 +46204,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1740" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1740" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1741" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8587,10 +8587,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8599,10 +8599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8610,10 +8610,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8622,10 +8622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -19167,7 +19167,7 @@
         <x:v>618</x:v>
       </x:c>
       <x:c r="B565" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C565" s="1">
         <x:v>0</x:v>
@@ -19179,10 +19179,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F565" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="G565" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
     </x:row>
     <x:row r="566" spans="1:7">
@@ -19190,7 +19190,7 @@
         <x:v>618</x:v>
       </x:c>
       <x:c r="B566" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C566" s="1">
         <x:v>0</x:v>
@@ -19202,10 +19202,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F566" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
       <x:c r="G566" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
     </x:row>
     <x:row r="567" spans="1:7">
@@ -43294,10 +43294,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43306,10 +43306,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -43317,10 +43317,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1615" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1615" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1615" s="1">
         <x:v>0</x:v>
@@ -43329,10 +43329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1615" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1615" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1616" spans="1:7">
@@ -44076,10 +44076,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44088,10 +44088,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -44099,10 +44099,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1649" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1649" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1649" s="1">
         <x:v>0</x:v>
@@ -44111,10 +44111,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1649" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1649" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1650" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -46169,10 +46169,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1739" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1739" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1739" s="1">
         <x:v>0</x:v>
@@ -46181,10 +46181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1739" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1739" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1740" spans="1:7">
@@ -46192,10 +46192,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1740" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1740" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1740" s="1">
         <x:v>0</x:v>
@@ -46204,10 +46204,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1740" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1740" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1741" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">
@@ -49688,10 +49688,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1892" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1892" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1892" s="1">
         <x:v>0</x:v>
@@ -49700,10 +49700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1892" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1892" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1893" spans="1:7">
@@ -49711,10 +49711,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1893" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1893" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1893" s="1">
         <x:v>0</x:v>
@@ -49723,10 +49723,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1893" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1893" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1894" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -17166,10 +17166,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -17178,10 +17178,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -17189,10 +17189,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B479" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C479" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D479" s="1">
         <x:v>0</x:v>
@@ -17201,10 +17201,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F479" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G479" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="480" spans="1:7">
@@ -19167,7 +19167,7 @@
         <x:v>618</x:v>
       </x:c>
       <x:c r="B565" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C565" s="1">
         <x:v>0</x:v>
@@ -19179,10 +19179,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F565" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
       <x:c r="G565" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
     </x:row>
     <x:row r="566" spans="1:7">
@@ -19190,7 +19190,7 @@
         <x:v>618</x:v>
       </x:c>
       <x:c r="B566" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C566" s="1">
         <x:v>0</x:v>
@@ -19202,10 +19202,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F566" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="G566" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
     </x:row>
     <x:row r="567" spans="1:7">
@@ -22065,10 +22065,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -22077,10 +22077,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -22088,10 +22088,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C692" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D692" s="1">
         <x:v>0</x:v>
@@ -22100,10 +22100,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -31035,10 +31035,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1081" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1081" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1081" s="1">
         <x:v>0</x:v>
@@ -31047,10 +31047,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1081" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1081" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1082" spans="1:7">
@@ -31058,10 +31058,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1082" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C1082" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1082" s="1">
         <x:v>0</x:v>
@@ -31070,10 +31070,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1082" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1082" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1083" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -44536,10 +44536,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1668" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1668" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1668" s="1">
         <x:v>0</x:v>
@@ -44548,10 +44548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1668" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1668" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1669" spans="1:7">
@@ -44559,10 +44559,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1669" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1669" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1669" s="1">
         <x:v>0</x:v>
@@ -44571,10 +44571,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1669" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1669" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1670" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -46169,10 +46169,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1739" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1739" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1739" s="1">
         <x:v>0</x:v>
@@ -46181,10 +46181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1739" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1739" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1740" spans="1:7">
@@ -46192,10 +46192,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1740" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1740" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1740" s="1">
         <x:v>0</x:v>
@@ -46204,10 +46204,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1740" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1740" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1741" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -17166,10 +17166,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -17178,10 +17178,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -17189,10 +17189,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B479" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C479" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D479" s="1">
         <x:v>0</x:v>
@@ -17201,10 +17201,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F479" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G479" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="480" spans="1:7">
@@ -22065,10 +22065,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -22077,10 +22077,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -22088,10 +22088,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C692" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D692" s="1">
         <x:v>0</x:v>
@@ -22100,10 +22100,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -31035,10 +31035,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1081" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C1081" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1081" s="1">
         <x:v>0</x:v>
@@ -31047,10 +31047,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1081" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1081" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1082" spans="1:7">
@@ -31058,10 +31058,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1082" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1082" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1082" s="1">
         <x:v>0</x:v>
@@ -31070,10 +31070,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1082" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1082" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1083" spans="1:7">
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -43294,10 +43294,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43306,10 +43306,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -43317,10 +43317,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1615" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1615" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1615" s="1">
         <x:v>0</x:v>
@@ -43329,10 +43329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1615" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1615" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1616" spans="1:7">
@@ -44536,10 +44536,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1668" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1668" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1668" s="1">
         <x:v>0</x:v>
@@ -44548,10 +44548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1668" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1668" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1669" spans="1:7">
@@ -44559,10 +44559,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1669" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1669" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1669" s="1">
         <x:v>0</x:v>
@@ -44571,10 +44571,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1669" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1669" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1670" spans="1:7">
@@ -46169,10 +46169,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1739" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1739" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1739" s="1">
         <x:v>0</x:v>
@@ -46181,10 +46181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1739" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1739" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1740" spans="1:7">
@@ -46192,10 +46192,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1740" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1740" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1740" s="1">
         <x:v>0</x:v>
@@ -46204,10 +46204,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1740" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1740" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1741" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">
@@ -49688,10 +49688,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1892" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1892" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1892" s="1">
         <x:v>0</x:v>
@@ -49700,10 +49700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1892" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1892" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1893" spans="1:7">
@@ -49711,10 +49711,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1893" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1893" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1893" s="1">
         <x:v>0</x:v>
@@ -49723,10 +49723,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1893" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1893" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1894" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8587,10 +8587,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8599,10 +8599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8610,10 +8610,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8622,10 +8622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -22065,10 +22065,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -22077,10 +22077,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -22088,10 +22088,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C692" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D692" s="1">
         <x:v>0</x:v>
@@ -22100,10 +22100,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -44076,10 +44076,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44088,10 +44088,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -44099,10 +44099,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1649" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1649" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1649" s="1">
         <x:v>0</x:v>
@@ -44111,10 +44111,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1649" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1649" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1650" spans="1:7">
@@ -46169,10 +46169,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1739" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1739" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1739" s="1">
         <x:v>0</x:v>
@@ -46181,10 +46181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1739" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1739" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1740" spans="1:7">
@@ -46192,10 +46192,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1740" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1740" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1740" s="1">
         <x:v>0</x:v>
@@ -46204,10 +46204,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1740" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1740" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1741" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8587,10 +8587,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8599,10 +8599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8610,10 +8610,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8622,10 +8622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -22065,10 +22065,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -22077,10 +22077,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -22088,10 +22088,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C692" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D692" s="1">
         <x:v>0</x:v>
@@ -22100,10 +22100,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -32576,10 +32576,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1148" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1148" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1148" s="1">
         <x:v>0</x:v>
@@ -32588,10 +32588,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1148" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1148" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1149" spans="1:7">
@@ -32599,10 +32599,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1149" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1149" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1149" s="1">
         <x:v>0</x:v>
@@ -32611,10 +32611,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1149" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1149" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1150" spans="1:7">
@@ -37682,10 +37682,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37694,10 +37694,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -37705,10 +37705,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1371" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1371" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1371" s="1">
         <x:v>0</x:v>
@@ -37717,10 +37717,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1371" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1371" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1372" spans="1:7">
@@ -43294,10 +43294,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43306,10 +43306,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -43317,10 +43317,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1615" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1615" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1615" s="1">
         <x:v>0</x:v>
@@ -43329,10 +43329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1615" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1615" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1616" spans="1:7">
@@ -44076,10 +44076,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44088,10 +44088,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -44099,10 +44099,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1649" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1649" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1649" s="1">
         <x:v>0</x:v>
@@ -44111,10 +44111,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1649" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1649" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1650" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">
@@ -49688,10 +49688,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1892" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1892" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1892" s="1">
         <x:v>0</x:v>
@@ -49700,10 +49700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1892" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1892" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1893" spans="1:7">
@@ -49711,10 +49711,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1893" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1893" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1893" s="1">
         <x:v>0</x:v>
@@ -49723,10 +49723,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1893" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1893" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1894" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8587,10 +8587,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8599,10 +8599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8610,10 +8610,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8622,10 +8622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -30437,10 +30437,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30449,10 +30449,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -30460,10 +30460,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1056" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1056" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1056" s="1">
         <x:v>0</x:v>
@@ -30472,10 +30472,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1056" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1056" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1057" spans="1:7">
@@ -32576,10 +32576,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1148" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1148" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1148" s="1">
         <x:v>0</x:v>
@@ -32588,10 +32588,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1148" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1148" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1149" spans="1:7">
@@ -32599,10 +32599,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1149" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1149" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1149" s="1">
         <x:v>0</x:v>
@@ -32611,10 +32611,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1149" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1149" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1150" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -43294,10 +43294,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43306,10 +43306,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -43317,10 +43317,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1615" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1615" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1615" s="1">
         <x:v>0</x:v>
@@ -43329,10 +43329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1615" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1615" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1616" spans="1:7">
@@ -45824,10 +45824,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1724" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1724" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1724" s="1">
         <x:v>0</x:v>
@@ -45836,10 +45836,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1724" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1724" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1725" spans="1:7">
@@ -45847,10 +45847,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1725" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1725" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1725" s="1">
         <x:v>0</x:v>
@@ -45859,10 +45859,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1725" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1725" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1726" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -46169,10 +46169,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1739" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1739" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1739" s="1">
         <x:v>0</x:v>
@@ -46181,10 +46181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1739" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1739" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1740" spans="1:7">
@@ -46192,10 +46192,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1740" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1740" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1740" s="1">
         <x:v>0</x:v>
@@ -46204,10 +46204,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1740" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1740" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1741" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -25561,10 +25561,10 @@
         <x:v>892</x:v>
       </x:c>
       <x:c r="B843" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C843" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D843" s="1">
         <x:v>0</x:v>
@@ -25573,10 +25573,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F843" s="1">
-        <x:v>7300</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G843" s="1">
-        <x:v>84580</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="844" spans="1:7">
@@ -25584,10 +25584,10 @@
         <x:v>892</x:v>
       </x:c>
       <x:c r="B844" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C844" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D844" s="1">
         <x:v>0</x:v>
@@ -25596,10 +25596,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F844" s="1">
-        <x:v>5342</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="G844" s="1">
-        <x:v>5342</x:v>
+        <x:v>84580</x:v>
       </x:c>
     </x:row>
     <x:row r="845" spans="1:7">
@@ -30437,10 +30437,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30449,10 +30449,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -30460,10 +30460,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1056" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1056" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1056" s="1">
         <x:v>0</x:v>
@@ -30472,10 +30472,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1056" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1056" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1057" spans="1:7">
@@ -32576,10 +32576,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1148" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1148" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1148" s="1">
         <x:v>0</x:v>
@@ -32588,10 +32588,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1148" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1148" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1149" spans="1:7">
@@ -32599,10 +32599,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1149" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1149" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1149" s="1">
         <x:v>0</x:v>
@@ -32611,10 +32611,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1149" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1149" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1150" spans="1:7">
@@ -37682,10 +37682,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37694,10 +37694,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -37705,10 +37705,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1371" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1371" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1371" s="1">
         <x:v>0</x:v>
@@ -37717,10 +37717,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1371" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1371" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1372" spans="1:7">
@@ -44076,10 +44076,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44088,10 +44088,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -44099,10 +44099,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1649" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1649" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1649" s="1">
         <x:v>0</x:v>
@@ -44111,10 +44111,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1649" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1649" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1650" spans="1:7">
@@ -44536,10 +44536,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1668" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1668" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1668" s="1">
         <x:v>0</x:v>
@@ -44548,10 +44548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1668" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1668" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1669" spans="1:7">
@@ -44559,10 +44559,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1669" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1669" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1669" s="1">
         <x:v>0</x:v>
@@ -44571,10 +44571,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1669" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1669" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1670" spans="1:7">
@@ -45824,10 +45824,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1724" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1724" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1724" s="1">
         <x:v>0</x:v>
@@ -45836,10 +45836,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1724" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1724" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1725" spans="1:7">
@@ -45847,10 +45847,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1725" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1725" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1725" s="1">
         <x:v>0</x:v>
@@ -45859,10 +45859,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1725" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1725" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1726" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8587,10 +8587,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8599,10 +8599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8610,10 +8610,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8622,10 +8622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -17166,10 +17166,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -17178,10 +17178,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -17189,10 +17189,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B479" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C479" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D479" s="1">
         <x:v>0</x:v>
@@ -17201,10 +17201,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F479" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G479" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="480" spans="1:7">
@@ -20317,10 +20317,10 @@
         <x:v>667</x:v>
       </x:c>
       <x:c r="B615" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C615" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D615" s="1">
         <x:v>0</x:v>
@@ -20329,10 +20329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F615" s="1">
-        <x:v>0</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G615" s="1">
-        <x:v>3500</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="616" spans="1:7">
@@ -20340,10 +20340,10 @@
         <x:v>667</x:v>
       </x:c>
       <x:c r="B616" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C616" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D616" s="1">
         <x:v>0</x:v>
@@ -20352,10 +20352,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F616" s="1">
-        <x:v>43</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G616" s="1">
-        <x:v>43</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="617" spans="1:7">
@@ -25561,10 +25561,10 @@
         <x:v>892</x:v>
       </x:c>
       <x:c r="B843" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C843" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D843" s="1">
         <x:v>0</x:v>
@@ -25573,10 +25573,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F843" s="1">
-        <x:v>5342</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="G843" s="1">
-        <x:v>5342</x:v>
+        <x:v>84580</x:v>
       </x:c>
     </x:row>
     <x:row r="844" spans="1:7">
@@ -25584,10 +25584,10 @@
         <x:v>892</x:v>
       </x:c>
       <x:c r="B844" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C844" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D844" s="1">
         <x:v>0</x:v>
@@ -25596,10 +25596,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F844" s="1">
-        <x:v>7300</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G844" s="1">
-        <x:v>84580</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="845" spans="1:7">
@@ -32576,10 +32576,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1148" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1148" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1148" s="1">
         <x:v>0</x:v>
@@ -32588,10 +32588,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1148" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1148" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1149" spans="1:7">
@@ -32599,10 +32599,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1149" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1149" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1149" s="1">
         <x:v>0</x:v>
@@ -32611,10 +32611,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1149" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1149" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1150" spans="1:7">
@@ -35221,22 +35221,22 @@
         <x:v>1306</x:v>
       </x:c>
       <x:c r="B1263" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C1263" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D1263" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E1263" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F1263" s="1">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="D1263" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E1263" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F1263" s="1">
-        <x:v>6400</x:v>
-      </x:c>
       <x:c r="G1263" s="1">
-        <x:v>11400</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1264" spans="1:7">
@@ -35244,10 +35244,10 @@
         <x:v>1306</x:v>
       </x:c>
       <x:c r="B1264" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1264" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1264" s="1">
         <x:v>0</x:v>
@@ -35256,10 +35256,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1264" s="1">
-        <x:v>5000</x:v>
+        <x:v>6400</x:v>
       </x:c>
       <x:c r="G1264" s="1">
-        <x:v>5000</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="1265" spans="1:7">
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -46169,10 +46169,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1739" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1739" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1739" s="1">
         <x:v>0</x:v>
@@ -46181,10 +46181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1739" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1739" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1740" spans="1:7">
@@ -46192,10 +46192,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1740" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1740" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1740" s="1">
         <x:v>0</x:v>
@@ -46204,10 +46204,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1740" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1740" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1741" spans="1:7">
@@ -49688,10 +49688,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1892" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1892" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1892" s="1">
         <x:v>0</x:v>
@@ -49700,10 +49700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1892" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1892" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1893" spans="1:7">
@@ -49711,10 +49711,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1893" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1893" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1893" s="1">
         <x:v>0</x:v>
@@ -49723,10 +49723,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1893" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1893" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1894" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -20317,10 +20317,10 @@
         <x:v>667</x:v>
       </x:c>
       <x:c r="B615" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C615" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D615" s="1">
         <x:v>0</x:v>
@@ -20329,10 +20329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F615" s="1">
-        <x:v>43</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G615" s="1">
-        <x:v>43</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="616" spans="1:7">
@@ -20340,10 +20340,10 @@
         <x:v>667</x:v>
       </x:c>
       <x:c r="B616" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C616" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D616" s="1">
         <x:v>0</x:v>
@@ -20352,10 +20352,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F616" s="1">
-        <x:v>0</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G616" s="1">
-        <x:v>3500</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="617" spans="1:7">
@@ -32576,10 +32576,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1148" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1148" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1148" s="1">
         <x:v>0</x:v>
@@ -32588,10 +32588,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1148" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1148" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1149" spans="1:7">
@@ -32599,10 +32599,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1149" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1149" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1149" s="1">
         <x:v>0</x:v>
@@ -32611,10 +32611,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1149" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1149" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1150" spans="1:7">
@@ -35221,10 +35221,10 @@
         <x:v>1306</x:v>
       </x:c>
       <x:c r="B1263" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1263" s="1">
-        <x:v>0</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1263" s="1">
         <x:v>0</x:v>
@@ -35233,10 +35233,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1263" s="1">
-        <x:v>5000</x:v>
+        <x:v>6400</x:v>
       </x:c>
       <x:c r="G1263" s="1">
-        <x:v>5000</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="1264" spans="1:7">
@@ -35244,22 +35244,22 @@
         <x:v>1306</x:v>
       </x:c>
       <x:c r="B1264" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C1264" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="D1264" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E1264" s="1">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F1264" s="1">
         <x:v>5000</x:v>
       </x:c>
-      <x:c r="D1264" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="E1264" s="1">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="F1264" s="1">
-        <x:v>6400</x:v>
-      </x:c>
       <x:c r="G1264" s="1">
-        <x:v>11400</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1265" spans="1:7">
@@ -37682,10 +37682,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37694,10 +37694,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -37705,10 +37705,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1371" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1371" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1371" s="1">
         <x:v>0</x:v>
@@ -37717,10 +37717,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1371" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1371" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1372" spans="1:7">
@@ -43294,10 +43294,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43306,10 +43306,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -43317,10 +43317,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1615" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1615" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1615" s="1">
         <x:v>0</x:v>
@@ -43329,10 +43329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1615" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1615" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1616" spans="1:7">
@@ -44076,10 +44076,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44088,10 +44088,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -44099,10 +44099,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1649" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1649" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1649" s="1">
         <x:v>0</x:v>
@@ -44111,10 +44111,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1649" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1649" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1650" spans="1:7">
@@ -44536,10 +44536,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1668" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1668" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1668" s="1">
         <x:v>0</x:v>
@@ -44548,10 +44548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1668" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1668" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1669" spans="1:7">
@@ -44559,10 +44559,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1669" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1669" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1669" s="1">
         <x:v>0</x:v>
@@ -44571,10 +44571,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1669" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1669" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1670" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -46169,10 +46169,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1739" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1739" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1739" s="1">
         <x:v>0</x:v>
@@ -46181,10 +46181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1739" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1739" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1740" spans="1:7">
@@ -46192,10 +46192,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1740" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1740" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1740" s="1">
         <x:v>0</x:v>
@@ -46204,10 +46204,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1740" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1740" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1741" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">
@@ -49688,10 +49688,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1892" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1892" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1892" s="1">
         <x:v>0</x:v>
@@ -49700,10 +49700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1892" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1892" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1893" spans="1:7">
@@ -49711,10 +49711,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1893" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1893" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1893" s="1">
         <x:v>0</x:v>
@@ -49723,10 +49723,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1893" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1893" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1894" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8587,10 +8587,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8599,10 +8599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8610,10 +8610,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8622,10 +8622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -17166,10 +17166,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -17178,10 +17178,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -17189,10 +17189,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B479" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C479" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D479" s="1">
         <x:v>0</x:v>
@@ -17201,10 +17201,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F479" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G479" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="480" spans="1:7">
@@ -25561,10 +25561,10 @@
         <x:v>892</x:v>
       </x:c>
       <x:c r="B843" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C843" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D843" s="1">
         <x:v>0</x:v>
@@ -25573,10 +25573,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F843" s="1">
-        <x:v>7300</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G843" s="1">
-        <x:v>84580</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="844" spans="1:7">
@@ -25584,10 +25584,10 @@
         <x:v>892</x:v>
       </x:c>
       <x:c r="B844" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C844" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D844" s="1">
         <x:v>0</x:v>
@@ -25596,10 +25596,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F844" s="1">
-        <x:v>5342</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="G844" s="1">
-        <x:v>5342</x:v>
+        <x:v>84580</x:v>
       </x:c>
     </x:row>
     <x:row r="845" spans="1:7">
@@ -32576,10 +32576,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1148" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1148" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1148" s="1">
         <x:v>0</x:v>
@@ -32588,10 +32588,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1148" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1148" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1149" spans="1:7">
@@ -32599,10 +32599,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1149" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1149" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1149" s="1">
         <x:v>0</x:v>
@@ -32611,10 +32611,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1149" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1149" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1150" spans="1:7">
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -37682,10 +37682,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37694,10 +37694,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -37705,10 +37705,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1371" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1371" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1371" s="1">
         <x:v>0</x:v>
@@ -37717,10 +37717,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1371" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1371" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1372" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -44502,10 +44502,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1666" s="1">
-        <x:v>7000</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="G1666" s="1">
-        <x:v>7000</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1667" spans="1:7">
@@ -44536,10 +44536,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1668" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1668" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1668" s="1">
         <x:v>0</x:v>
@@ -44548,10 +44548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1668" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1668" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1669" spans="1:7">
@@ -44559,10 +44559,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1669" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1669" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1669" s="1">
         <x:v>0</x:v>
@@ -44571,10 +44571,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1669" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1669" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1670" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">
@@ -49688,10 +49688,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1892" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1892" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1892" s="1">
         <x:v>0</x:v>
@@ -49700,10 +49700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1892" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1892" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1893" spans="1:7">
@@ -49711,10 +49711,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1893" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1893" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1893" s="1">
         <x:v>0</x:v>
@@ -49723,10 +49723,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1893" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1893" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1894" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -22065,10 +22065,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -22077,10 +22077,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -22088,10 +22088,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C692" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D692" s="1">
         <x:v>0</x:v>
@@ -22100,10 +22100,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -25561,10 +25561,10 @@
         <x:v>892</x:v>
       </x:c>
       <x:c r="B843" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C843" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D843" s="1">
         <x:v>0</x:v>
@@ -25573,10 +25573,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F843" s="1">
-        <x:v>5342</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="G843" s="1">
-        <x:v>5342</x:v>
+        <x:v>84580</x:v>
       </x:c>
     </x:row>
     <x:row r="844" spans="1:7">
@@ -25584,10 +25584,10 @@
         <x:v>892</x:v>
       </x:c>
       <x:c r="B844" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C844" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D844" s="1">
         <x:v>0</x:v>
@@ -25596,10 +25596,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F844" s="1">
-        <x:v>7300</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G844" s="1">
-        <x:v>84580</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="845" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -44076,10 +44076,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44088,10 +44088,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -44099,10 +44099,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1649" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1649" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1649" s="1">
         <x:v>0</x:v>
@@ -44111,10 +44111,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1649" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1649" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1650" spans="1:7">
@@ -44536,10 +44536,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1668" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1668" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1668" s="1">
         <x:v>0</x:v>
@@ -44548,10 +44548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1668" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1668" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1669" spans="1:7">
@@ -44559,10 +44559,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1669" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1669" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1669" s="1">
         <x:v>0</x:v>
@@ -44571,10 +44571,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1669" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1669" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1670" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8587,10 +8587,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8599,10 +8599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8610,10 +8610,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8622,10 +8622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -17166,10 +17166,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -17178,10 +17178,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -17189,10 +17189,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B479" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C479" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D479" s="1">
         <x:v>0</x:v>
@@ -17201,10 +17201,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F479" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G479" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="480" spans="1:7">
@@ -22065,10 +22065,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -22077,10 +22077,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -22088,10 +22088,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C692" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D692" s="1">
         <x:v>0</x:v>
@@ -22100,10 +22100,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -37682,10 +37682,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37694,10 +37694,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -37705,10 +37705,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1371" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1371" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1371" s="1">
         <x:v>0</x:v>
@@ -37717,10 +37717,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1371" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1371" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1372" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -43294,10 +43294,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43306,10 +43306,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -43317,10 +43317,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1615" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1615" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1615" s="1">
         <x:v>0</x:v>
@@ -43329,10 +43329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1615" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1615" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1616" spans="1:7">
@@ -44076,10 +44076,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44088,10 +44088,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -44099,10 +44099,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1649" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1649" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1649" s="1">
         <x:v>0</x:v>
@@ -44111,10 +44111,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1649" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1649" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1650" spans="1:7">
@@ -44536,10 +44536,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1668" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1668" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1668" s="1">
         <x:v>0</x:v>
@@ -44548,10 +44548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1668" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1668" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1669" spans="1:7">
@@ -44559,10 +44559,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1669" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1669" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1669" s="1">
         <x:v>0</x:v>
@@ -44571,10 +44571,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1669" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1669" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1670" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -46169,10 +46169,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1739" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1739" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1739" s="1">
         <x:v>0</x:v>
@@ -46181,10 +46181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1739" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1739" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1740" spans="1:7">
@@ -46192,10 +46192,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1740" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1740" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1740" s="1">
         <x:v>0</x:v>
@@ -46204,10 +46204,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1740" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1740" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1741" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -17166,10 +17166,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -17178,10 +17178,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -17189,10 +17189,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B479" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C479" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D479" s="1">
         <x:v>0</x:v>
@@ -17201,10 +17201,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F479" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G479" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="480" spans="1:7">
@@ -32576,10 +32576,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1148" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1148" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1148" s="1">
         <x:v>0</x:v>
@@ -32588,10 +32588,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1148" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1148" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1149" spans="1:7">
@@ -32599,10 +32599,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1149" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1149" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1149" s="1">
         <x:v>0</x:v>
@@ -32611,10 +32611,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1149" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1149" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1150" spans="1:7">
@@ -44536,10 +44536,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1668" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1668" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1668" s="1">
         <x:v>0</x:v>
@@ -44548,10 +44548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1668" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1668" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1669" spans="1:7">
@@ -44559,10 +44559,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1669" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1669" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1669" s="1">
         <x:v>0</x:v>
@@ -44571,10 +44571,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1669" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1669" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1670" spans="1:7">
@@ -46169,10 +46169,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1739" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1739" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1739" s="1">
         <x:v>0</x:v>
@@ -46181,10 +46181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1739" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1739" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1740" spans="1:7">
@@ -46192,10 +46192,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1740" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1740" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1740" s="1">
         <x:v>0</x:v>
@@ -46204,10 +46204,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1740" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1740" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1741" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -30437,10 +30437,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30449,10 +30449,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -30460,10 +30460,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1056" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1056" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1056" s="1">
         <x:v>0</x:v>
@@ -30472,10 +30472,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1056" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1056" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1057" spans="1:7">
@@ -32576,10 +32576,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1148" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1148" s="1">
-        <x:v>0</x:v>
+        <x:v>170640</x:v>
       </x:c>
       <x:c r="D1148" s="1">
         <x:v>0</x:v>
@@ -32588,10 +32588,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1148" s="1">
-        <x:v>5000</x:v>
+        <x:v>58425</x:v>
       </x:c>
       <x:c r="G1148" s="1">
-        <x:v>5000</x:v>
+        <x:v>229065</x:v>
       </x:c>
     </x:row>
     <x:row r="1149" spans="1:7">
@@ -32599,10 +32599,10 @@
         <x:v>1192</x:v>
       </x:c>
       <x:c r="B1149" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1149" s="1">
-        <x:v>170640</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1149" s="1">
         <x:v>0</x:v>
@@ -32611,10 +32611,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1149" s="1">
-        <x:v>58425</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="G1149" s="1">
-        <x:v>229065</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1150" spans="1:7">
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -45824,10 +45824,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1724" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1724" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1724" s="1">
         <x:v>0</x:v>
@@ -45836,10 +45836,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1724" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1724" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1725" spans="1:7">
@@ -45847,10 +45847,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1725" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1725" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1725" s="1">
         <x:v>0</x:v>
@@ -45859,10 +45859,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1725" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1725" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1726" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -30437,10 +30437,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30449,10 +30449,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -30460,10 +30460,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1056" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1056" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1056" s="1">
         <x:v>0</x:v>
@@ -30472,10 +30472,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1056" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1056" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1057" spans="1:7">
@@ -37682,10 +37682,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37694,10 +37694,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -37705,10 +37705,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1371" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1371" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1371" s="1">
         <x:v>0</x:v>
@@ -37717,10 +37717,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1371" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1371" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1372" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -43294,10 +43294,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43306,10 +43306,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -43317,10 +43317,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1615" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1615" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1615" s="1">
         <x:v>0</x:v>
@@ -43329,10 +43329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1615" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1615" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1616" spans="1:7">
@@ -45824,10 +45824,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1724" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1724" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1724" s="1">
         <x:v>0</x:v>
@@ -45836,10 +45836,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1724" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1724" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1725" spans="1:7">
@@ -45847,10 +45847,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1725" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1725" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1725" s="1">
         <x:v>0</x:v>
@@ -45859,10 +45859,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1725" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1725" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1726" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -30437,10 +30437,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30449,10 +30449,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -30460,10 +30460,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1056" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1056" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1056" s="1">
         <x:v>0</x:v>
@@ -30472,10 +30472,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1056" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1056" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1057" spans="1:7">
@@ -31035,10 +31035,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1081" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1081" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1081" s="1">
         <x:v>0</x:v>
@@ -31047,10 +31047,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1081" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1081" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1082" spans="1:7">
@@ -31058,10 +31058,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1082" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C1082" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1082" s="1">
         <x:v>0</x:v>
@@ -31070,10 +31070,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1082" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1082" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1083" spans="1:7">
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -37682,10 +37682,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37694,10 +37694,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -37705,10 +37705,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1371" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1371" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1371" s="1">
         <x:v>0</x:v>
@@ -37717,10 +37717,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1371" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1371" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1372" spans="1:7">
@@ -45824,10 +45824,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1724" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1724" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1724" s="1">
         <x:v>0</x:v>
@@ -45836,10 +45836,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1724" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1724" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1725" spans="1:7">
@@ -45847,10 +45847,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1725" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1725" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1725" s="1">
         <x:v>0</x:v>
@@ -45859,10 +45859,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1725" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1725" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1726" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -6276,10 +6276,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F4" s="1">
-        <x:v>3900</x:v>
+        <x:v>7400</x:v>
       </x:c>
       <x:c r="G4" s="1">
-        <x:v>3900</x:v>
+        <x:v>7400</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:7">
@@ -8587,10 +8587,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8599,10 +8599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8610,10 +8610,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8622,10 +8622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -22065,10 +22065,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -22077,10 +22077,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -22088,10 +22088,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C692" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D692" s="1">
         <x:v>0</x:v>
@@ -22100,10 +22100,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -30437,10 +30437,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30449,10 +30449,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -30460,10 +30460,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1056" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1056" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1056" s="1">
         <x:v>0</x:v>
@@ -30472,10 +30472,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1056" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1056" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1057" spans="1:7">
@@ -31035,10 +31035,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1081" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C1081" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1081" s="1">
         <x:v>0</x:v>
@@ -31047,10 +31047,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1081" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1081" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1082" spans="1:7">
@@ -31058,10 +31058,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1082" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1082" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1082" s="1">
         <x:v>0</x:v>
@@ -31070,10 +31070,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1082" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1082" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1083" spans="1:7">
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -37682,10 +37682,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37694,10 +37694,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -37705,10 +37705,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1371" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1371" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1371" s="1">
         <x:v>0</x:v>
@@ -37717,10 +37717,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1371" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1371" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1372" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -44076,10 +44076,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44088,10 +44088,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -44099,10 +44099,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1649" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1649" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1649" s="1">
         <x:v>0</x:v>
@@ -44111,10 +44111,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1649" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1649" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1650" spans="1:7">
@@ -45824,10 +45824,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1724" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C1724" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1724" s="1">
         <x:v>0</x:v>
@@ -45836,10 +45836,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1724" s="1">
-        <x:v>3300</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1724" s="1">
-        <x:v>3300</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1725" spans="1:7">
@@ -45847,10 +45847,10 @@
         <x:v>1758</x:v>
       </x:c>
       <x:c r="B1725" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1725" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1725" s="1">
         <x:v>0</x:v>
@@ -45859,10 +45859,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1725" s="1">
-        <x:v>0</x:v>
+        <x:v>3300</x:v>
       </x:c>
       <x:c r="G1725" s="1">
-        <x:v>2500</x:v>
+        <x:v>3300</x:v>
       </x:c>
     </x:row>
     <x:row r="1726" spans="1:7">
@@ -49688,10 +49688,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1892" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1892" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1892" s="1">
         <x:v>0</x:v>
@@ -49700,10 +49700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1892" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1892" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1893" spans="1:7">
@@ -49711,10 +49711,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1893" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1893" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1893" s="1">
         <x:v>0</x:v>
@@ -49723,10 +49723,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1893" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1893" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1894" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8587,10 +8587,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8599,10 +8599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8610,10 +8610,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8622,10 +8622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -17166,10 +17166,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -17178,10 +17178,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -17189,10 +17189,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B479" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C479" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D479" s="1">
         <x:v>0</x:v>
@@ -17201,10 +17201,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F479" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G479" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="480" spans="1:7">
@@ -22065,10 +22065,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -22077,10 +22077,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -22088,10 +22088,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C692" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D692" s="1">
         <x:v>0</x:v>
@@ -22100,10 +22100,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -36302,7 +36302,7 @@
         <x:v>1352</x:v>
       </x:c>
       <x:c r="B1310" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1310" s="1">
         <x:v>0</x:v>
@@ -36314,10 +36314,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1310" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1310" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1311" spans="1:7">
@@ -36325,7 +36325,7 @@
         <x:v>1352</x:v>
       </x:c>
       <x:c r="B1311" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1311" s="1">
         <x:v>0</x:v>
@@ -36337,10 +36337,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1311" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1311" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1312" spans="1:7">
@@ -41546,7 +41546,7 @@
         <x:v>1577</x:v>
       </x:c>
       <x:c r="B1538" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1538" s="1">
         <x:v>0</x:v>
@@ -41558,10 +41558,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1538" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
       <x:c r="G1538" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
     </x:row>
     <x:row r="1539" spans="1:7">
@@ -41569,7 +41569,7 @@
         <x:v>1577</x:v>
       </x:c>
       <x:c r="B1539" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C1539" s="1">
         <x:v>0</x:v>
@@ -41581,10 +41581,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1539" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1539" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1540" spans="1:7">
@@ -43294,10 +43294,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1614" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C1614" s="1">
-        <x:v>34590</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="D1614" s="1">
         <x:v>0</x:v>
@@ -43306,10 +43306,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1614" s="1">
-        <x:v>4850</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1614" s="1">
-        <x:v>39440</x:v>
+        <x:v>2000</x:v>
       </x:c>
     </x:row>
     <x:row r="1615" spans="1:7">
@@ -43317,10 +43317,10 @@
         <x:v>1651</x:v>
       </x:c>
       <x:c r="B1615" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1615" s="1">
-        <x:v>2000</x:v>
+        <x:v>34590</x:v>
       </x:c>
       <x:c r="D1615" s="1">
         <x:v>0</x:v>
@@ -43329,10 +43329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1615" s="1">
-        <x:v>0</x:v>
+        <x:v>4850</x:v>
       </x:c>
       <x:c r="G1615" s="1">
-        <x:v>2000</x:v>
+        <x:v>39440</x:v>
       </x:c>
     </x:row>
     <x:row r="1616" spans="1:7">
@@ -44076,10 +44076,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44088,10 +44088,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -44099,10 +44099,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1649" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1649" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1649" s="1">
         <x:v>0</x:v>
@@ -44111,10 +44111,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1649" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1649" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1650" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -19167,7 +19167,7 @@
         <x:v>618</x:v>
       </x:c>
       <x:c r="B565" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C565" s="1">
         <x:v>0</x:v>
@@ -19179,10 +19179,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F565" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="G565" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
     </x:row>
     <x:row r="566" spans="1:7">
@@ -19190,7 +19190,7 @@
         <x:v>618</x:v>
       </x:c>
       <x:c r="B566" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C566" s="1">
         <x:v>0</x:v>
@@ -19202,10 +19202,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F566" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
       <x:c r="G566" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
     </x:row>
     <x:row r="567" spans="1:7">
@@ -28022,10 +28022,10 @@
         <x:v>997</x:v>
       </x:c>
       <x:c r="B950" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C950" s="1">
-        <x:v>32500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D950" s="1">
         <x:v>0</x:v>
@@ -28034,10 +28034,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F950" s="1">
-        <x:v>20000</x:v>
+        <x:v>118100</x:v>
       </x:c>
       <x:c r="G950" s="1">
-        <x:v>52500</x:v>
+        <x:v>118100</x:v>
       </x:c>
     </x:row>
     <x:row r="951" spans="1:7">
@@ -28045,10 +28045,10 @@
         <x:v>997</x:v>
       </x:c>
       <x:c r="B951" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C951" s="1">
-        <x:v>0</x:v>
+        <x:v>32500</x:v>
       </x:c>
       <x:c r="D951" s="1">
         <x:v>0</x:v>
@@ -28057,10 +28057,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F951" s="1">
-        <x:v>118100</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="G951" s="1">
-        <x:v>118100</x:v>
+        <x:v>52500</x:v>
       </x:c>
     </x:row>
     <x:row r="952" spans="1:7">
@@ -36302,7 +36302,7 @@
         <x:v>1352</x:v>
       </x:c>
       <x:c r="B1310" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1310" s="1">
         <x:v>0</x:v>
@@ -36314,10 +36314,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1310" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1310" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1311" spans="1:7">
@@ -36325,7 +36325,7 @@
         <x:v>1352</x:v>
       </x:c>
       <x:c r="B1311" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1311" s="1">
         <x:v>0</x:v>
@@ -36337,10 +36337,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1311" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1311" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1312" spans="1:7">
@@ -41546,7 +41546,7 @@
         <x:v>1577</x:v>
       </x:c>
       <x:c r="B1538" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C1538" s="1">
         <x:v>0</x:v>
@@ -41558,10 +41558,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1538" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1538" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1539" spans="1:7">
@@ -41569,7 +41569,7 @@
         <x:v>1577</x:v>
       </x:c>
       <x:c r="B1539" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1539" s="1">
         <x:v>0</x:v>
@@ -41581,10 +41581,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1539" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
       <x:c r="G1539" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
     </x:row>
     <x:row r="1540" spans="1:7">
@@ -44076,10 +44076,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44088,10 +44088,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -44099,10 +44099,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1649" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1649" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1649" s="1">
         <x:v>0</x:v>
@@ -44111,10 +44111,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1649" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1649" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1650" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -17166,10 +17166,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -17178,10 +17178,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -17189,10 +17189,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B479" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C479" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D479" s="1">
         <x:v>0</x:v>
@@ -17201,10 +17201,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F479" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G479" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="480" spans="1:7">
@@ -19167,7 +19167,7 @@
         <x:v>618</x:v>
       </x:c>
       <x:c r="B565" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C565" s="1">
         <x:v>0</x:v>
@@ -19179,10 +19179,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F565" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
       <x:c r="G565" s="1">
-        <x:v>750</x:v>
+        <x:v>3050</x:v>
       </x:c>
     </x:row>
     <x:row r="566" spans="1:7">
@@ -19190,7 +19190,7 @@
         <x:v>618</x:v>
       </x:c>
       <x:c r="B566" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C566" s="1">
         <x:v>0</x:v>
@@ -19202,10 +19202,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F566" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
       <x:c r="G566" s="1">
-        <x:v>3050</x:v>
+        <x:v>750</x:v>
       </x:c>
     </x:row>
     <x:row r="567" spans="1:7">
@@ -28022,10 +28022,10 @@
         <x:v>997</x:v>
       </x:c>
       <x:c r="B950" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C950" s="1">
-        <x:v>0</x:v>
+        <x:v>32500</x:v>
       </x:c>
       <x:c r="D950" s="1">
         <x:v>0</x:v>
@@ -28034,10 +28034,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F950" s="1">
-        <x:v>118100</x:v>
+        <x:v>20000</x:v>
       </x:c>
       <x:c r="G950" s="1">
-        <x:v>118100</x:v>
+        <x:v>52500</x:v>
       </x:c>
     </x:row>
     <x:row r="951" spans="1:7">
@@ -28045,10 +28045,10 @@
         <x:v>997</x:v>
       </x:c>
       <x:c r="B951" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C951" s="1">
-        <x:v>32500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D951" s="1">
         <x:v>0</x:v>
@@ -28057,10 +28057,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F951" s="1">
-        <x:v>20000</x:v>
+        <x:v>118100</x:v>
       </x:c>
       <x:c r="G951" s="1">
-        <x:v>52500</x:v>
+        <x:v>118100</x:v>
       </x:c>
     </x:row>
     <x:row r="952" spans="1:7">
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -44076,10 +44076,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44088,10 +44088,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -44099,10 +44099,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1649" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1649" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1649" s="1">
         <x:v>0</x:v>
@@ -44111,10 +44111,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1649" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1649" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1650" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -37682,10 +37682,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37694,10 +37694,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -37705,10 +37705,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1371" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1371" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1371" s="1">
         <x:v>0</x:v>
@@ -37717,10 +37717,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1371" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1371" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1372" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -49688,10 +49688,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1892" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1892" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1892" s="1">
         <x:v>0</x:v>
@@ -49700,10 +49700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1892" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1892" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1893" spans="1:7">
@@ -49711,10 +49711,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1893" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1893" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1893" s="1">
         <x:v>0</x:v>
@@ -49723,10 +49723,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1893" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1893" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1894" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -37682,10 +37682,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1370" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C1370" s="1">
-        <x:v>0</x:v>
+        <x:v>24000</x:v>
       </x:c>
       <x:c r="D1370" s="1">
         <x:v>0</x:v>
@@ -37694,10 +37694,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>1000</x:v>
       </x:c>
       <x:c r="G1370" s="1">
-        <x:v>6600</x:v>
+        <x:v>25000</x:v>
       </x:c>
     </x:row>
     <x:row r="1371" spans="1:7">
@@ -37705,10 +37705,10 @@
         <x:v>1410</x:v>
       </x:c>
       <x:c r="B1371" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1371" s="1">
-        <x:v>24000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1371" s="1">
         <x:v>0</x:v>
@@ -37717,10 +37717,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1371" s="1">
-        <x:v>1000</x:v>
+        <x:v>6600</x:v>
       </x:c>
       <x:c r="G1371" s="1">
-        <x:v>25000</x:v>
+        <x:v>6600</x:v>
       </x:c>
     </x:row>
     <x:row r="1372" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8587,10 +8587,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8599,10 +8599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8610,10 +8610,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8622,10 +8622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -22065,10 +22065,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -22077,10 +22077,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -22088,10 +22088,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C692" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D692" s="1">
         <x:v>0</x:v>
@@ -22100,10 +22100,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -30437,10 +30437,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30449,10 +30449,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -30460,10 +30460,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1056" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1056" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1056" s="1">
         <x:v>0</x:v>
@@ -30472,10 +30472,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1056" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1056" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1057" spans="1:7">
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">
@@ -49688,10 +49688,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1892" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1892" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1892" s="1">
         <x:v>0</x:v>
@@ -49700,10 +49700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1892" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1892" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1893" spans="1:7">
@@ -49711,10 +49711,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1893" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1893" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1893" s="1">
         <x:v>0</x:v>
@@ -49723,10 +49723,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1893" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1893" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1894" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -8587,10 +8587,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B105" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C105" s="1">
-        <x:v>0</x:v>
+        <x:v>55700</x:v>
       </x:c>
       <x:c r="D105" s="1">
         <x:v>0</x:v>
@@ -8599,10 +8599,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F105" s="1">
-        <x:v>2800</x:v>
+        <x:v>20849</x:v>
       </x:c>
       <x:c r="G105" s="1">
-        <x:v>2800</x:v>
+        <x:v>76549</x:v>
       </x:c>
     </x:row>
     <x:row r="106" spans="1:7">
@@ -8610,10 +8610,10 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B106" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C106" s="1">
-        <x:v>55700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D106" s="1">
         <x:v>0</x:v>
@@ -8622,10 +8622,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F106" s="1">
-        <x:v>20849</x:v>
+        <x:v>2800</x:v>
       </x:c>
       <x:c r="G106" s="1">
-        <x:v>76549</x:v>
+        <x:v>2800</x:v>
       </x:c>
     </x:row>
     <x:row r="107" spans="1:7">
@@ -22065,10 +22065,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B691" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="C691" s="1">
-        <x:v>0</x:v>
+        <x:v>5250</x:v>
       </x:c>
       <x:c r="D691" s="1">
         <x:v>0</x:v>
@@ -22077,10 +22077,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F691" s="1">
-        <x:v>2700</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G691" s="1">
-        <x:v>2700</x:v>
+        <x:v>5250</x:v>
       </x:c>
     </x:row>
     <x:row r="692" spans="1:7">
@@ -22088,10 +22088,10 @@
         <x:v>741</x:v>
       </x:c>
       <x:c r="B692" s="1" t="s">
-        <x:v>243</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C692" s="1">
-        <x:v>5250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D692" s="1">
         <x:v>0</x:v>
@@ -22100,10 +22100,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F692" s="1">
-        <x:v>0</x:v>
+        <x:v>2700</x:v>
       </x:c>
       <x:c r="G692" s="1">
-        <x:v>5250</x:v>
+        <x:v>2700</x:v>
       </x:c>
     </x:row>
     <x:row r="693" spans="1:7">
@@ -30437,10 +30437,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1055" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C1055" s="1">
-        <x:v>0</x:v>
+        <x:v>13000</x:v>
       </x:c>
       <x:c r="D1055" s="1">
         <x:v>0</x:v>
@@ -30449,10 +30449,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>12750</x:v>
       </x:c>
       <x:c r="G1055" s="1">
-        <x:v>15500</x:v>
+        <x:v>25750</x:v>
       </x:c>
     </x:row>
     <x:row r="1056" spans="1:7">
@@ -30460,10 +30460,10 @@
         <x:v>1101</x:v>
       </x:c>
       <x:c r="B1056" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1056" s="1">
-        <x:v>13000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1056" s="1">
         <x:v>0</x:v>
@@ -30472,10 +30472,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1056" s="1">
-        <x:v>12750</x:v>
+        <x:v>15500</x:v>
       </x:c>
       <x:c r="G1056" s="1">
-        <x:v>25750</x:v>
+        <x:v>15500</x:v>
       </x:c>
     </x:row>
     <x:row r="1057" spans="1:7">
@@ -31035,10 +31035,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1081" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1081" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1081" s="1">
         <x:v>0</x:v>
@@ -31047,10 +31047,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1081" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1081" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1082" spans="1:7">
@@ -31058,10 +31058,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1082" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C1082" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1082" s="1">
         <x:v>0</x:v>
@@ -31070,10 +31070,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1082" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1082" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1083" spans="1:7">
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -44076,10 +44076,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44088,10 +44088,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -44099,10 +44099,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1649" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1649" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1649" s="1">
         <x:v>0</x:v>
@@ -44111,10 +44111,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1649" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1649" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1650" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -17166,10 +17166,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -17178,10 +17178,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -17189,10 +17189,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B479" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C479" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D479" s="1">
         <x:v>0</x:v>
@@ -17201,10 +17201,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F479" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G479" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="480" spans="1:7">
@@ -31035,10 +31035,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1081" s="1" t="s">
-        <x:v>21</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C1081" s="1">
-        <x:v>49500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1081" s="1">
         <x:v>0</x:v>
@@ -31047,10 +31047,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1081" s="1">
-        <x:v>2000</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1081" s="1">
-        <x:v>51500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1082" spans="1:7">
@@ -31058,10 +31058,10 @@
         <x:v>1126</x:v>
       </x:c>
       <x:c r="B1082" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C1082" s="1">
-        <x:v>2500</x:v>
+        <x:v>49500</x:v>
       </x:c>
       <x:c r="D1082" s="1">
         <x:v>0</x:v>
@@ -31070,10 +31070,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1082" s="1">
-        <x:v>0</x:v>
+        <x:v>2000</x:v>
       </x:c>
       <x:c r="G1082" s="1">
-        <x:v>2500</x:v>
+        <x:v>51500</x:v>
       </x:c>
     </x:row>
     <x:row r="1083" spans="1:7">
@@ -36302,7 +36302,7 @@
         <x:v>1352</x:v>
       </x:c>
       <x:c r="B1310" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1310" s="1">
         <x:v>0</x:v>
@@ -36314,10 +36314,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1310" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1310" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1311" spans="1:7">
@@ -36325,7 +36325,7 @@
         <x:v>1352</x:v>
       </x:c>
       <x:c r="B1311" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1311" s="1">
         <x:v>0</x:v>
@@ -36337,10 +36337,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1311" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1311" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1312" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -41546,7 +41546,7 @@
         <x:v>1577</x:v>
       </x:c>
       <x:c r="B1538" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1538" s="1">
         <x:v>0</x:v>
@@ -41558,10 +41558,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1538" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
       <x:c r="G1538" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
     </x:row>
     <x:row r="1539" spans="1:7">
@@ -41569,7 +41569,7 @@
         <x:v>1577</x:v>
       </x:c>
       <x:c r="B1539" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C1539" s="1">
         <x:v>0</x:v>
@@ -41581,10 +41581,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1539" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1539" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1540" spans="1:7">
@@ -44076,10 +44076,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44088,10 +44088,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -44099,10 +44099,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1649" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1649" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1649" s="1">
         <x:v>0</x:v>
@@ -44111,10 +44111,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1649" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1649" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1650" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">
@@ -49688,10 +49688,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1892" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1892" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1892" s="1">
         <x:v>0</x:v>
@@ -49700,10 +49700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1892" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1892" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1893" spans="1:7">
@@ -49711,10 +49711,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1893" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1893" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1893" s="1">
         <x:v>0</x:v>
@@ -49723,10 +49723,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1893" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1893" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1894" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -25561,10 +25561,10 @@
         <x:v>892</x:v>
       </x:c>
       <x:c r="B843" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C843" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D843" s="1">
         <x:v>0</x:v>
@@ -25573,10 +25573,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F843" s="1">
-        <x:v>7300</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G843" s="1">
-        <x:v>84580</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="844" spans="1:7">
@@ -25584,10 +25584,10 @@
         <x:v>892</x:v>
       </x:c>
       <x:c r="B844" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C844" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D844" s="1">
         <x:v>0</x:v>
@@ -25596,10 +25596,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F844" s="1">
-        <x:v>5342</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="G844" s="1">
-        <x:v>5342</x:v>
+        <x:v>84580</x:v>
       </x:c>
     </x:row>
     <x:row r="845" spans="1:7">
@@ -35865,10 +35865,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1291" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>20500</x:v>
       </x:c>
       <x:c r="D1291" s="1">
         <x:v>0</x:v>
@@ -35877,10 +35877,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1291" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1291" s="1">
-        <x:v>2500</x:v>
+        <x:v>21000</x:v>
       </x:c>
     </x:row>
     <x:row r="1292" spans="1:7">
@@ -35888,10 +35888,10 @@
         <x:v>1333</x:v>
       </x:c>
       <x:c r="B1292" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C1292" s="1">
-        <x:v>20500</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1292" s="1">
         <x:v>0</x:v>
@@ -35900,10 +35900,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1292" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1292" s="1">
-        <x:v>21000</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1293" spans="1:7">
@@ -36302,7 +36302,7 @@
         <x:v>1352</x:v>
       </x:c>
       <x:c r="B1310" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C1310" s="1">
         <x:v>0</x:v>
@@ -36314,10 +36314,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1310" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
       <x:c r="G1310" s="1">
-        <x:v>220</x:v>
+        <x:v>3200</x:v>
       </x:c>
     </x:row>
     <x:row r="1311" spans="1:7">
@@ -36325,7 +36325,7 @@
         <x:v>1352</x:v>
       </x:c>
       <x:c r="B1311" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1311" s="1">
         <x:v>0</x:v>
@@ -36337,10 +36337,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1311" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="G1311" s="1">
-        <x:v>3200</x:v>
+        <x:v>220</x:v>
       </x:c>
     </x:row>
     <x:row r="1312" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -41546,7 +41546,7 @@
         <x:v>1577</x:v>
       </x:c>
       <x:c r="B1538" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C1538" s="1">
         <x:v>0</x:v>
@@ -41558,10 +41558,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1538" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1538" s="1">
-        <x:v>3539</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1539" spans="1:7">
@@ -41569,7 +41569,7 @@
         <x:v>1577</x:v>
       </x:c>
       <x:c r="B1539" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1539" s="1">
         <x:v>0</x:v>
@@ -41581,10 +41581,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1539" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
       <x:c r="G1539" s="1">
-        <x:v>500</x:v>
+        <x:v>3539</x:v>
       </x:c>
     </x:row>
     <x:row r="1540" spans="1:7">
@@ -44076,10 +44076,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44088,10 +44088,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -44099,10 +44099,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1649" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1649" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1649" s="1">
         <x:v>0</x:v>
@@ -44111,10 +44111,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1649" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1649" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1650" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -46169,10 +46169,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1739" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1739" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1739" s="1">
         <x:v>0</x:v>
@@ -46181,10 +46181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1739" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1739" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1740" spans="1:7">
@@ -46192,10 +46192,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1740" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1740" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1740" s="1">
         <x:v>0</x:v>
@@ -46204,10 +46204,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1740" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1740" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1741" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">
@@ -49688,10 +49688,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1892" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C1892" s="1">
-        <x:v>2500</x:v>
+        <x:v>28300</x:v>
       </x:c>
       <x:c r="D1892" s="1">
         <x:v>0</x:v>
@@ -49700,10 +49700,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1892" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1892" s="1">
-        <x:v>2500</x:v>
+        <x:v>28800</x:v>
       </x:c>
     </x:row>
     <x:row r="1893" spans="1:7">
@@ -49711,10 +49711,10 @@
         <x:v>1921</x:v>
       </x:c>
       <x:c r="B1893" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1893" s="1">
-        <x:v>28300</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1893" s="1">
         <x:v>0</x:v>
@@ -49723,10 +49723,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1893" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1893" s="1">
-        <x:v>28800</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1894" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -20317,10 +20317,10 @@
         <x:v>667</x:v>
       </x:c>
       <x:c r="B615" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C615" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D615" s="1">
         <x:v>0</x:v>
@@ -20329,10 +20329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F615" s="1">
-        <x:v>0</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G615" s="1">
-        <x:v>3500</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="616" spans="1:7">
@@ -20340,10 +20340,10 @@
         <x:v>667</x:v>
       </x:c>
       <x:c r="B616" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C616" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D616" s="1">
         <x:v>0</x:v>
@@ -20352,10 +20352,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F616" s="1">
-        <x:v>43</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G616" s="1">
-        <x:v>43</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="617" spans="1:7">
@@ -25561,10 +25561,10 @@
         <x:v>892</x:v>
       </x:c>
       <x:c r="B843" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C843" s="1">
-        <x:v>0</x:v>
+        <x:v>77280</x:v>
       </x:c>
       <x:c r="D843" s="1">
         <x:v>0</x:v>
@@ -25573,10 +25573,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F843" s="1">
-        <x:v>5342</x:v>
+        <x:v>7300</x:v>
       </x:c>
       <x:c r="G843" s="1">
-        <x:v>5342</x:v>
+        <x:v>84580</x:v>
       </x:c>
     </x:row>
     <x:row r="844" spans="1:7">
@@ -25584,10 +25584,10 @@
         <x:v>892</x:v>
       </x:c>
       <x:c r="B844" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C844" s="1">
-        <x:v>77280</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D844" s="1">
         <x:v>0</x:v>
@@ -25596,10 +25596,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F844" s="1">
-        <x:v>7300</x:v>
+        <x:v>5342</x:v>
       </x:c>
       <x:c r="G844" s="1">
-        <x:v>84580</x:v>
+        <x:v>5342</x:v>
       </x:c>
     </x:row>
     <x:row r="845" spans="1:7">
@@ -40971,10 +40971,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1513" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C1513" s="1">
-        <x:v>34500</x:v>
+        <x:v>33500</x:v>
       </x:c>
       <x:c r="D1513" s="1">
         <x:v>0</x:v>
@@ -40983,10 +40983,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1513" s="1">
-        <x:v>4600</x:v>
+        <x:v>41325</x:v>
       </x:c>
       <x:c r="G1513" s="1">
-        <x:v>39100</x:v>
+        <x:v>74825</x:v>
       </x:c>
     </x:row>
     <x:row r="1514" spans="1:7">
@@ -40994,10 +40994,10 @@
         <x:v>1553</x:v>
       </x:c>
       <x:c r="B1514" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1514" s="1">
-        <x:v>33500</x:v>
+        <x:v>34500</x:v>
       </x:c>
       <x:c r="D1514" s="1">
         <x:v>0</x:v>
@@ -41006,10 +41006,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1514" s="1">
-        <x:v>41325</x:v>
+        <x:v>4600</x:v>
       </x:c>
       <x:c r="G1514" s="1">
-        <x:v>74825</x:v>
+        <x:v>39100</x:v>
       </x:c>
     </x:row>
     <x:row r="1515" spans="1:7">
@@ -44536,10 +44536,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1668" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1668" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1668" s="1">
         <x:v>0</x:v>
@@ -44548,10 +44548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1668" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1668" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1669" spans="1:7">
@@ -44559,10 +44559,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1669" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1669" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1669" s="1">
         <x:v>0</x:v>
@@ -44571,10 +44571,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1669" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1669" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1670" spans="1:7">

--- a/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
+++ b/reports/pro-big-tech/pro-big-tech-candidate-lobby-lifetime-report.xlsx
@@ -17166,10 +17166,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B478" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C478" s="1">
-        <x:v>0</x:v>
+        <x:v>13100</x:v>
       </x:c>
       <x:c r="D478" s="1">
         <x:v>0</x:v>
@@ -17178,10 +17178,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F478" s="1">
-        <x:v>11400</x:v>
+        <x:v>6950</x:v>
       </x:c>
       <x:c r="G478" s="1">
-        <x:v>11400</x:v>
+        <x:v>20050</x:v>
       </x:c>
     </x:row>
     <x:row r="479" spans="1:7">
@@ -17189,10 +17189,10 @@
         <x:v>532</x:v>
       </x:c>
       <x:c r="B479" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C479" s="1">
-        <x:v>13100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D479" s="1">
         <x:v>0</x:v>
@@ -17201,10 +17201,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F479" s="1">
-        <x:v>6950</x:v>
+        <x:v>11400</x:v>
       </x:c>
       <x:c r="G479" s="1">
-        <x:v>20050</x:v>
+        <x:v>11400</x:v>
       </x:c>
     </x:row>
     <x:row r="480" spans="1:7">
@@ -20317,10 +20317,10 @@
         <x:v>667</x:v>
       </x:c>
       <x:c r="B615" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C615" s="1">
-        <x:v>0</x:v>
+        <x:v>3500</x:v>
       </x:c>
       <x:c r="D615" s="1">
         <x:v>0</x:v>
@@ -20329,10 +20329,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F615" s="1">
-        <x:v>43</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G615" s="1">
-        <x:v>43</x:v>
+        <x:v>3500</x:v>
       </x:c>
     </x:row>
     <x:row r="616" spans="1:7">
@@ -20340,10 +20340,10 @@
         <x:v>667</x:v>
       </x:c>
       <x:c r="B616" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C616" s="1">
-        <x:v>3500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D616" s="1">
         <x:v>0</x:v>
@@ -20352,10 +20352,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F616" s="1">
-        <x:v>0</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="G616" s="1">
-        <x:v>3500</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="617" spans="1:7">
@@ -44076,10 +44076,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1648" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C1648" s="1">
-        <x:v>36500</x:v>
+        <x:v>7000</x:v>
       </x:c>
       <x:c r="D1648" s="1">
         <x:v>0</x:v>
@@ -44088,10 +44088,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1648" s="1">
-        <x:v>25250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1648" s="1">
-        <x:v>61750</x:v>
+        <x:v>7000</x:v>
       </x:c>
     </x:row>
     <x:row r="1649" spans="1:7">
@@ -44099,10 +44099,10 @@
         <x:v>1684</x:v>
       </x:c>
       <x:c r="B1649" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C1649" s="1">
-        <x:v>7000</x:v>
+        <x:v>36500</x:v>
       </x:c>
       <x:c r="D1649" s="1">
         <x:v>0</x:v>
@@ -44111,10 +44111,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1649" s="1">
-        <x:v>0</x:v>
+        <x:v>25250</x:v>
       </x:c>
       <x:c r="G1649" s="1">
-        <x:v>7000</x:v>
+        <x:v>61750</x:v>
       </x:c>
     </x:row>
     <x:row r="1650" spans="1:7">
@@ -44536,10 +44536,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1668" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1668" s="1">
-        <x:v>0</x:v>
+        <x:v>2500</x:v>
       </x:c>
       <x:c r="D1668" s="1">
         <x:v>0</x:v>
@@ -44548,10 +44548,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1668" s="1">
-        <x:v>500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1668" s="1">
-        <x:v>500</x:v>
+        <x:v>2500</x:v>
       </x:c>
     </x:row>
     <x:row r="1669" spans="1:7">
@@ -44559,10 +44559,10 @@
         <x:v>1703</x:v>
       </x:c>
       <x:c r="B1669" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C1669" s="1">
-        <x:v>2500</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D1669" s="1">
         <x:v>0</x:v>
@@ -44571,10 +44571,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1669" s="1">
-        <x:v>0</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="G1669" s="1">
-        <x:v>2500</x:v>
+        <x:v>500</x:v>
       </x:c>
     </x:row>
     <x:row r="1670" spans="1:7">
@@ -45985,10 +45985,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1731" s="1" t="s">
-        <x:v>478</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C1731" s="1">
-        <x:v>112640</x:v>
+        <x:v>5000</x:v>
       </x:c>
       <x:c r="D1731" s="1">
         <x:v>0</x:v>
@@ -45997,10 +45997,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1731" s="1">
-        <x:v>19800</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1731" s="1">
-        <x:v>132440</x:v>
+        <x:v>5000</x:v>
       </x:c>
     </x:row>
     <x:row r="1732" spans="1:7">
@@ -46008,10 +46008,10 @@
         <x:v>1764</x:v>
       </x:c>
       <x:c r="B1732" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="C1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>112640</x:v>
       </x:c>
       <x:c r="D1732" s="1">
         <x:v>0</x:v>
@@ -46020,10 +46020,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1732" s="1">
-        <x:v>0</x:v>
+        <x:v>19800</x:v>
       </x:c>
       <x:c r="G1732" s="1">
-        <x:v>5000</x:v>
+        <x:v>132440</x:v>
       </x:c>
     </x:row>
     <x:row r="1733" spans="1:7">
@@ -46169,10 +46169,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1739" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C1739" s="1">
-        <x:v>74280</x:v>
+        <x:v>7500</x:v>
       </x:c>
       <x:c r="D1739" s="1">
         <x:v>0</x:v>
@@ -46181,10 +46181,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1739" s="1">
-        <x:v>7250</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1739" s="1">
-        <x:v>81530</x:v>
+        <x:v>7500</x:v>
       </x:c>
     </x:row>
     <x:row r="1740" spans="1:7">
@@ -46192,10 +46192,10 @@
         <x:v>1771</x:v>
       </x:c>
       <x:c r="B1740" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C1740" s="1">
-        <x:v>7500</x:v>
+        <x:v>74280</x:v>
       </x:c>
       <x:c r="D1740" s="1">
         <x:v>0</x:v>
@@ -46204,10 +46204,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F1740" s="1">
-        <x:v>0</x:v>
+        <x:v>7250</x:v>
       </x:c>
       <x:c r="G1740" s="1">
-        <x:v>7500</x:v>
+        <x:v>81530</x:v>
       </x:c>
     </x:row>
     <x:row r="1741" spans="1:7">
@@ -47618,10 +47618,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1802" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
       <x:c r="D1802" s="1">
         <x:v>0</x:v>
@@ -47633,7 +47633,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1802" s="1">
-        <x:v>25500</x:v>
+        <x:v>8500</x:v>
       </x:c>
     </x:row>
     <x:row r="1803" spans="1:7">
@@ -47641,10 +47641,10 @@
         <x:v>1833</x:v>
       </x:c>
       <x:c r="B1803" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
       <x:c r="D1803" s="1">
         <x:v>0</x:v>
@@ -47656,7 +47656,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="G1803" s="1">
-        <x:v>8500</x:v>
+        <x:v>25500</x:v>
       </x:c>
     </x:row>
     <x:row r="1804" spans="1:7">
